--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124234435</v>
+        <v>124235016</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466046</v>
+        <v>466066</v>
       </c>
       <c r="R2" t="n">
-        <v>7054578</v>
+        <v>7054677</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -959,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124233387</v>
+        <v>124233251</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,42 +980,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466025</v>
+        <v>466029</v>
       </c>
       <c r="R4" t="n">
-        <v>7054632</v>
+        <v>7054550</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124235851</v>
+        <v>124235290</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1137,17 +1137,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466040</v>
+        <v>466069</v>
       </c>
       <c r="R5" t="n">
-        <v>7054923</v>
+        <v>7054731</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124229492</v>
+        <v>124233935</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,37 +1254,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466104</v>
+        <v>466049</v>
       </c>
       <c r="R6" t="n">
-        <v>7054370</v>
+        <v>7054622</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1318,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1323,7 +1328,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,12 +1362,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1375,10 +1385,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124238409</v>
+        <v>124238954</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1391,42 +1401,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466019</v>
+        <v>466048</v>
       </c>
       <c r="R7" t="n">
-        <v>7054696</v>
+        <v>7054406</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1465,12 +1470,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124231227</v>
+        <v>124234661</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466082</v>
+        <v>466088</v>
       </c>
       <c r="R8" t="n">
-        <v>7054428</v>
+        <v>7054654</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1659,7 +1659,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124236910</v>
+        <v>124236233</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1695,17 +1695,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466024</v>
+        <v>466113</v>
       </c>
       <c r="R9" t="n">
-        <v>7054965</v>
+        <v>7054849</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1796,7 +1796,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124232343</v>
+        <v>124234435</v>
       </c>
       <c r="B10" t="n">
         <v>91030</v>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466050</v>
+        <v>466046</v>
       </c>
       <c r="R10" t="n">
-        <v>7054470</v>
+        <v>7054578</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1886,12 +1886,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1920,12 +1915,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1943,7 +1938,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124238072</v>
+        <v>124236910</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1979,17 +1974,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466028</v>
+        <v>466024</v>
       </c>
       <c r="R11" t="n">
-        <v>7054700</v>
+        <v>7054965</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2018,7 +2013,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2028,7 +2023,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2080,10 +2075,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124233251</v>
+        <v>124231450</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2096,37 +2091,56 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466029</v>
+        <v>466113</v>
       </c>
       <c r="R12" t="n">
-        <v>7054550</v>
+        <v>7054408</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2155,7 +2169,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2165,7 +2179,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2180,26 +2199,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2217,10 +2216,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124237831</v>
+        <v>124238409</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2233,42 +2232,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466048</v>
+        <v>466019</v>
       </c>
       <c r="R13" t="n">
-        <v>7054795</v>
+        <v>7054696</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2297,7 +2296,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2307,7 +2306,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2336,12 +2340,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2359,10 +2363,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124236835</v>
+        <v>124235081</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2375,37 +2379,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466084</v>
+        <v>466058</v>
       </c>
       <c r="R14" t="n">
-        <v>7054927</v>
+        <v>7054681</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2432,19 +2441,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:21</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2473,12 +2477,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2496,10 +2500,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124235081</v>
+        <v>124238072</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2512,42 +2516,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466058</v>
+        <v>466028</v>
       </c>
       <c r="R15" t="n">
-        <v>7054681</v>
+        <v>7054700</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2574,14 +2573,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2610,12 +2614,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2633,10 +2637,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124235016</v>
+        <v>124238716</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2649,42 +2653,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466066</v>
+        <v>466019</v>
       </c>
       <c r="R16" t="n">
-        <v>7054677</v>
+        <v>7054567</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2713,7 +2712,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2723,12 +2722,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2757,12 +2751,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2780,10 +2774,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124234661</v>
+        <v>124229168</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2792,38 +2786,57 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466088</v>
+        <v>466061</v>
       </c>
       <c r="R17" t="n">
-        <v>7054654</v>
+        <v>7054409</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2855,7 +2868,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,7 +2878,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2880,26 +2893,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2917,10 +2910,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124231450</v>
+        <v>124237831</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2933,56 +2926,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466113</v>
+        <v>466048</v>
       </c>
       <c r="R18" t="n">
-        <v>7054408</v>
+        <v>7054795</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3011,7 +2990,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3021,12 +3000,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3041,6 +3015,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3058,10 +3052,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124233935</v>
+        <v>124236835</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3074,42 +3068,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466049</v>
+        <v>466084</v>
       </c>
       <c r="R19" t="n">
-        <v>7054622</v>
+        <v>7054927</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3138,7 +3127,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3148,12 +3137,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3182,12 +3166,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3205,7 +3189,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124236233</v>
+        <v>124237519</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -3241,17 +3225,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466113</v>
+        <v>466024</v>
       </c>
       <c r="R20" t="n">
-        <v>7054849</v>
+        <v>7054752</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3280,7 +3264,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3290,7 +3274,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3304,17 +3288,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3324,7 +3298,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3342,10 +3316,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124236594</v>
+        <v>124231227</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3354,60 +3328,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466108</v>
+        <v>466082</v>
       </c>
       <c r="R21" t="n">
-        <v>7054934</v>
+        <v>7054428</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3436,7 +3391,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3446,7 +3401,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3461,6 +3416,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3478,10 +3453,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124237519</v>
+        <v>124230947</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3490,41 +3465,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466024</v>
+        <v>466100</v>
       </c>
       <c r="R22" t="n">
-        <v>7054752</v>
+        <v>7054439</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3553,7 +3542,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3563,7 +3552,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3578,16 +3567,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3605,10 +3584,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124230947</v>
+        <v>124233387</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3617,40 +3596,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3659,13 +3629,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466100</v>
+        <v>466025</v>
       </c>
       <c r="R23" t="n">
-        <v>7054439</v>
+        <v>7054632</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3694,7 +3664,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3704,7 +3674,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3719,6 +3689,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3736,7 +3726,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124238716</v>
+        <v>124229492</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3776,13 +3766,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466019</v>
+        <v>466104</v>
       </c>
       <c r="R24" t="n">
-        <v>7054567</v>
+        <v>7054370</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3811,7 +3801,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3821,7 +3811,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3873,10 +3863,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124238954</v>
+        <v>124232343</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3889,37 +3879,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466048</v>
+        <v>466050</v>
       </c>
       <c r="R25" t="n">
-        <v>7054406</v>
+        <v>7054470</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3948,7 +3943,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3958,7 +3953,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124236542</v>
+        <v>124235507</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4026,37 +4026,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466114</v>
+        <v>466047</v>
       </c>
       <c r="R26" t="n">
-        <v>7054930</v>
+        <v>7054739</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4085,7 +4090,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4095,7 +4100,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4124,12 +4129,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4147,10 +4152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124229168</v>
+        <v>124236542</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4159,60 +4164,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466061</v>
+        <v>466114</v>
       </c>
       <c r="R27" t="n">
-        <v>7054409</v>
+        <v>7054930</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4241,7 +4227,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4251,7 +4237,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4266,6 +4252,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4283,7 +4289,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124235290</v>
+        <v>124235851</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -4319,17 +4325,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466069</v>
+        <v>466040</v>
       </c>
       <c r="R28" t="n">
-        <v>7054731</v>
+        <v>7054923</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4358,7 +4364,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4368,7 +4374,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4397,12 +4403,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4557,10 +4563,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124235507</v>
+        <v>124236594</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4569,43 +4575,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466047</v>
+        <v>466108</v>
       </c>
       <c r="R30" t="n">
-        <v>7054739</v>
+        <v>7054934</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4637,7 +4657,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4647,7 +4667,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4662,26 +4682,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124233675</v>
+        <v>124232050</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4738,19 +4738,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466039</v>
+        <v>466045</v>
       </c>
       <c r="R31" t="n">
-        <v>7054631</v>
+        <v>7054447</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4779,7 +4784,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4789,12 +4794,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4846,7 +4851,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124229096</v>
+        <v>124231120</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4880,27 +4885,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466061</v>
+        <v>466086</v>
       </c>
       <c r="R32" t="n">
-        <v>7054411</v>
+        <v>7054427</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4929,7 +4931,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4939,12 +4941,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4996,7 +4998,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124232050</v>
+        <v>124228388</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5032,12 +5034,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5046,13 +5043,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466045</v>
+        <v>466017</v>
       </c>
       <c r="R33" t="n">
-        <v>7054447</v>
+        <v>7054386</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5078,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5088,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5148,10 +5145,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124231714</v>
+        <v>124232959</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5164,27 +5161,32 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5193,13 +5195,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466077</v>
+        <v>466071</v>
       </c>
       <c r="R34" t="n">
-        <v>7054405</v>
+        <v>7054484</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5228,7 +5230,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5238,7 +5240,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5290,7 +5297,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124232609</v>
+        <v>124230274</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5324,31 +5331,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466085</v>
+        <v>466120</v>
       </c>
       <c r="R35" t="n">
-        <v>7054527</v>
+        <v>7054456</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124228388</v>
+        <v>124233428</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5460,16 +5460,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5480,7 +5480,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466017</v>
+        <v>466026</v>
       </c>
       <c r="R36" t="n">
-        <v>7054386</v>
+        <v>7054647</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5591,7 +5591,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124235393</v>
+        <v>124237622</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5632,17 +5632,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466051</v>
+        <v>466053</v>
       </c>
       <c r="R37" t="n">
-        <v>7054737</v>
+        <v>7054770</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5738,7 +5738,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124237940</v>
+        <v>124232609</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5772,6 +5772,8 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -5784,14 +5786,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466040</v>
+        <v>466085</v>
       </c>
       <c r="R38" t="n">
-        <v>7054768</v>
+        <v>7054527</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5823,7 +5825,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5833,12 +5835,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5890,7 +5892,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124228589</v>
+        <v>124229096</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5924,24 +5926,27 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466066</v>
+        <v>466061</v>
       </c>
       <c r="R39" t="n">
-        <v>7054389</v>
+        <v>7054411</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5970,7 +5975,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5980,12 +5985,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6037,7 +6042,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124232959</v>
+        <v>124228589</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6076,24 +6081,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466071</v>
+        <v>466066</v>
       </c>
       <c r="R40" t="n">
-        <v>7054484</v>
+        <v>7054389</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6189,7 +6189,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124231120</v>
+        <v>124228749</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6225,7 +6225,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466086</v>
+        <v>466066</v>
       </c>
       <c r="R41" t="n">
-        <v>7054427</v>
+        <v>7054397</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6336,7 +6336,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124230274</v>
+        <v>124236498</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6372,22 +6372,22 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466120</v>
+        <v>466123</v>
       </c>
       <c r="R42" t="n">
-        <v>7054456</v>
+        <v>7054939</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6483,10 +6483,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124237622</v>
+        <v>124231714</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6499,42 +6499,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466053</v>
+        <v>466077</v>
       </c>
       <c r="R43" t="n">
-        <v>7054770</v>
+        <v>7054405</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,12 +6573,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6630,7 +6625,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124228749</v>
+        <v>124233675</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6675,13 +6670,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466066</v>
+        <v>466039</v>
       </c>
       <c r="R44" t="n">
-        <v>7054397</v>
+        <v>7054631</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6705,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6715,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6777,7 +6772,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124236498</v>
+        <v>124237940</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6813,22 +6808,27 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466123</v>
+        <v>466040</v>
       </c>
       <c r="R45" t="n">
-        <v>7054939</v>
+        <v>7054768</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,10 +6924,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124233428</v>
+        <v>124235393</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6960,7 +6960,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466026</v>
+        <v>466051</v>
       </c>
       <c r="R46" t="n">
-        <v>7054647</v>
+        <v>7054737</v>
       </c>
       <c r="S46" t="n">
         <v>11</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124235016</v>
+        <v>124237519</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466066</v>
+        <v>466024</v>
       </c>
       <c r="R2" t="n">
-        <v>7054677</v>
+        <v>7054752</v>
       </c>
       <c r="S2" t="n">
         <v>12</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,24 +777,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124234049</v>
+        <v>124233387</v>
       </c>
       <c r="B3" t="n">
         <v>91030</v>
@@ -867,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466057</v>
+        <v>466025</v>
       </c>
       <c r="R3" t="n">
-        <v>7054600</v>
+        <v>7054632</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124233251</v>
+        <v>124230947</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -976,41 +956,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466029</v>
+        <v>466100</v>
       </c>
       <c r="R4" t="n">
-        <v>7054550</v>
+        <v>7054439</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1033,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,7 +1043,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,26 +1058,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124235290</v>
+        <v>124235081</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,37 +1091,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466069</v>
+        <v>466058</v>
       </c>
       <c r="R5" t="n">
-        <v>7054731</v>
+        <v>7054681</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1174,19 +1153,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:37</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1238,7 +1212,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124233935</v>
+        <v>124232343</v>
       </c>
       <c r="B6" t="n">
         <v>91030</v>
@@ -1283,13 +1257,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466049</v>
+        <v>466050</v>
       </c>
       <c r="R6" t="n">
-        <v>7054622</v>
+        <v>7054470</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1318,7 +1292,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1328,12 +1302,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1385,7 +1359,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124238954</v>
+        <v>124235290</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1425,13 +1399,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466048</v>
+        <v>466069</v>
       </c>
       <c r="R7" t="n">
-        <v>7054406</v>
+        <v>7054731</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1460,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1470,7 +1444,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1499,12 +1473,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1522,7 +1496,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124234661</v>
+        <v>124231227</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1562,13 +1536,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466088</v>
+        <v>466082</v>
       </c>
       <c r="R8" t="n">
-        <v>7054654</v>
+        <v>7054428</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1571,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,7 +1581,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1659,7 +1633,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124236233</v>
+        <v>124234661</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1695,14 +1669,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466113</v>
+        <v>466088</v>
       </c>
       <c r="R9" t="n">
-        <v>7054849</v>
+        <v>7054654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1734,7 +1708,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1744,7 +1718,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,7 +1732,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1796,10 +1770,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124234435</v>
+        <v>124238072</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1812,42 +1786,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466046</v>
+        <v>466028</v>
       </c>
       <c r="R10" t="n">
-        <v>7054578</v>
+        <v>7054700</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1876,7 +1845,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1886,7 +1855,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1915,12 +1884,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1938,10 +1907,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124236910</v>
+        <v>124235507</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1954,34 +1923,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466024</v>
+        <v>466047</v>
       </c>
       <c r="R11" t="n">
-        <v>7054965</v>
+        <v>7054739</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -2013,7 +1987,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2023,7 +1997,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2052,12 +2026,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2075,10 +2049,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124231450</v>
+        <v>124233935</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2091,41 +2065,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2134,13 +2094,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466113</v>
+        <v>466049</v>
       </c>
       <c r="R12" t="n">
-        <v>7054408</v>
+        <v>7054622</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2169,7 +2129,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2179,12 +2139,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2199,6 +2159,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2216,10 +2196,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124238409</v>
+        <v>124233251</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2232,42 +2212,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466019</v>
+        <v>466029</v>
       </c>
       <c r="R13" t="n">
-        <v>7054696</v>
+        <v>7054550</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2296,7 +2271,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2306,12 +2281,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2340,12 +2310,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2363,10 +2333,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124235081</v>
+        <v>124229492</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2379,39 +2349,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466058</v>
+        <v>466104</v>
       </c>
       <c r="R14" t="n">
-        <v>7054681</v>
+        <v>7054370</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2441,14 +2406,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2477,12 +2447,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2500,10 +2470,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124238072</v>
+        <v>124229168</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2512,41 +2482,60 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466028</v>
+        <v>466061</v>
       </c>
       <c r="R15" t="n">
-        <v>7054700</v>
+        <v>7054409</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2575,7 +2564,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2585,7 +2574,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2600,26 +2589,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2637,10 +2606,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124238716</v>
+        <v>124231450</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2653,37 +2622,56 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466019</v>
+        <v>466113</v>
       </c>
       <c r="R16" t="n">
-        <v>7054567</v>
+        <v>7054408</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2712,7 +2700,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2722,7 +2710,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2737,26 +2730,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2774,10 +2747,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124229168</v>
+        <v>124238716</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2786,60 +2759,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466061</v>
+        <v>466019</v>
       </c>
       <c r="R17" t="n">
-        <v>7054409</v>
+        <v>7054567</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2868,7 +2822,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2878,7 +2832,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2893,6 +2847,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2910,10 +2884,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124237831</v>
+        <v>124235851</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2926,42 +2900,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466048</v>
+        <v>466040</v>
       </c>
       <c r="R18" t="n">
-        <v>7054795</v>
+        <v>7054923</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2990,7 +2959,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3000,7 +2969,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3029,12 +2998,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3052,7 +3021,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124236835</v>
+        <v>124233335</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -3088,17 +3057,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466084</v>
+        <v>466029</v>
       </c>
       <c r="R19" t="n">
-        <v>7054927</v>
+        <v>7054621</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3127,7 +3096,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3137,7 +3106,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3189,10 +3158,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124237519</v>
+        <v>124235016</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3205,34 +3174,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466024</v>
+        <v>466066</v>
       </c>
       <c r="R20" t="n">
-        <v>7054752</v>
+        <v>7054677</v>
       </c>
       <c r="S20" t="n">
         <v>12</v>
@@ -3264,7 +3238,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3274,7 +3248,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3291,14 +3270,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3316,10 +3305,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124231227</v>
+        <v>124236594</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3328,41 +3317,60 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466082</v>
+        <v>466108</v>
       </c>
       <c r="R21" t="n">
-        <v>7054428</v>
+        <v>7054934</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3391,7 +3399,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3401,7 +3409,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3416,26 +3424,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3453,10 +3441,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124230947</v>
+        <v>124238954</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3465,55 +3453,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466100</v>
+        <v>466048</v>
       </c>
       <c r="R22" t="n">
-        <v>7054439</v>
+        <v>7054406</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3542,7 +3516,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3552,7 +3526,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3567,6 +3541,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3584,10 +3578,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124233387</v>
+        <v>124236835</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3600,42 +3594,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466025</v>
+        <v>466084</v>
       </c>
       <c r="R23" t="n">
-        <v>7054632</v>
+        <v>7054927</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3664,7 +3653,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3674,7 +3663,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3703,12 +3692,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3726,10 +3715,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124229492</v>
+        <v>124237831</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3742,37 +3731,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466104</v>
+        <v>466048</v>
       </c>
       <c r="R24" t="n">
-        <v>7054370</v>
+        <v>7054795</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3801,7 +3795,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3811,7 +3805,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3840,12 +3834,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3863,10 +3857,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232343</v>
+        <v>124236910</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3879,42 +3873,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466050</v>
+        <v>466024</v>
       </c>
       <c r="R25" t="n">
-        <v>7054470</v>
+        <v>7054965</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3943,7 +3932,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3953,12 +3942,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3987,12 +3971,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4010,10 +3994,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124235507</v>
+        <v>124238409</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4026,27 +4010,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4055,10 +4039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466047</v>
+        <v>466019</v>
       </c>
       <c r="R26" t="n">
-        <v>7054739</v>
+        <v>7054696</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -4090,7 +4074,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4100,7 +4084,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4289,10 +4278,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124235851</v>
+        <v>124234435</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4305,37 +4294,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466040</v>
+        <v>466046</v>
       </c>
       <c r="R28" t="n">
-        <v>7054923</v>
+        <v>7054578</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4364,7 +4358,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4374,7 +4368,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4403,12 +4397,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4426,7 +4420,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124233335</v>
+        <v>124236233</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -4462,17 +4456,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466029</v>
+        <v>466113</v>
       </c>
       <c r="R29" t="n">
-        <v>7054621</v>
+        <v>7054849</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4501,7 +4495,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4511,7 +4505,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4525,7 +4519,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4563,10 +4557,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124236594</v>
+        <v>124234049</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4575,57 +4569,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466108</v>
+        <v>466057</v>
       </c>
       <c r="R30" t="n">
-        <v>7054934</v>
+        <v>7054600</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4657,7 +4637,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4667,7 +4647,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4682,6 +4662,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124232050</v>
+        <v>124230274</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4738,24 +4738,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466045</v>
+        <v>466120</v>
       </c>
       <c r="R31" t="n">
-        <v>7054447</v>
+        <v>7054456</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4784,7 +4779,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4794,12 +4789,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4851,7 +4846,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124231120</v>
+        <v>124233675</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4887,7 +4882,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4896,13 +4891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466086</v>
+        <v>466039</v>
       </c>
       <c r="R32" t="n">
-        <v>7054427</v>
+        <v>7054631</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4931,7 +4926,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4941,12 +4936,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4998,10 +4993,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124228388</v>
+        <v>124231714</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5014,27 +5009,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5043,10 +5038,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466017</v>
+        <v>466077</v>
       </c>
       <c r="R33" t="n">
-        <v>7054386</v>
+        <v>7054405</v>
       </c>
       <c r="S33" t="n">
         <v>7</v>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5088,12 +5083,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5145,7 +5135,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124232959</v>
+        <v>124232050</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5181,7 +5171,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5195,13 +5185,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466071</v>
+        <v>466045</v>
       </c>
       <c r="R34" t="n">
-        <v>7054484</v>
+        <v>7054447</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5230,7 +5220,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5240,12 +5230,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5297,7 +5287,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124230274</v>
+        <v>124228749</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5342,13 +5332,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466120</v>
+        <v>466066</v>
       </c>
       <c r="R35" t="n">
-        <v>7054456</v>
+        <v>7054397</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5377,7 +5367,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5387,12 +5377,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5444,10 +5434,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124233428</v>
+        <v>124232609</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5460,16 +5450,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5478,24 +5468,31 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466026</v>
+        <v>466085</v>
       </c>
       <c r="R36" t="n">
-        <v>7054647</v>
+        <v>7054527</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5524,7 +5521,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5534,12 +5531,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5738,7 +5735,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124232609</v>
+        <v>124237940</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5772,8 +5769,6 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -5786,14 +5781,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466085</v>
+        <v>466040</v>
       </c>
       <c r="R38" t="n">
-        <v>7054527</v>
+        <v>7054768</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5825,7 +5820,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5835,12 +5830,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5892,7 +5887,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124229096</v>
+        <v>124236498</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5926,24 +5921,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466061</v>
+        <v>466123</v>
       </c>
       <c r="R39" t="n">
-        <v>7054411</v>
+        <v>7054939</v>
       </c>
       <c r="S39" t="n">
         <v>12</v>
@@ -5975,7 +5967,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5985,12 +5977,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6042,7 +6034,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124228589</v>
+        <v>124229096</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6076,24 +6068,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466066</v>
+        <v>466061</v>
       </c>
       <c r="R40" t="n">
-        <v>7054389</v>
+        <v>7054411</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6122,7 +6117,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6132,12 +6127,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6189,10 +6184,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124228749</v>
+        <v>124233428</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6205,16 +6200,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6234,13 +6229,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466066</v>
+        <v>466026</v>
       </c>
       <c r="R41" t="n">
-        <v>7054397</v>
+        <v>7054647</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6269,7 +6264,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6279,12 +6274,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6336,7 +6331,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124236498</v>
+        <v>124231120</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6377,17 +6372,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466123</v>
+        <v>466086</v>
       </c>
       <c r="R42" t="n">
-        <v>7054939</v>
+        <v>7054427</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6426,12 +6421,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6483,10 +6478,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124231714</v>
+        <v>124228388</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6499,27 +6494,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6528,10 +6523,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466077</v>
+        <v>466017</v>
       </c>
       <c r="R43" t="n">
-        <v>7054405</v>
+        <v>7054386</v>
       </c>
       <c r="S43" t="n">
         <v>7</v>
@@ -6563,7 +6558,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,7 +6568,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6625,7 +6625,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124233675</v>
+        <v>124235393</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6661,7 +6661,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466039</v>
+        <v>466051</v>
       </c>
       <c r="R44" t="n">
-        <v>7054631</v>
+        <v>7054737</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6772,7 +6772,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124237940</v>
+        <v>124228589</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6808,24 +6808,19 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466040</v>
+        <v>466066</v>
       </c>
       <c r="R45" t="n">
-        <v>7054768</v>
+        <v>7054389</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -6857,7 +6852,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6862,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6919,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124235393</v>
+        <v>124232959</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6963,19 +6958,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466051</v>
+        <v>466071</v>
       </c>
       <c r="R46" t="n">
-        <v>7054737</v>
+        <v>7054484</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124237519</v>
+        <v>124236542</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466024</v>
+        <v>466114</v>
       </c>
       <c r="R2" t="n">
-        <v>7054752</v>
+        <v>7054930</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +777,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -784,7 +794,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124233387</v>
+        <v>124234435</v>
       </c>
       <c r="B3" t="n">
         <v>91030</v>
@@ -847,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466025</v>
+        <v>466046</v>
       </c>
       <c r="R3" t="n">
-        <v>7054632</v>
+        <v>7054578</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124230947</v>
+        <v>124229492</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,55 +966,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466100</v>
+        <v>466104</v>
       </c>
       <c r="R4" t="n">
-        <v>7054439</v>
+        <v>7054370</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1043,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,6 +1054,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1075,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124235081</v>
+        <v>124229168</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,31 +1103,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1120,13 +1150,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466058</v>
+        <v>466061</v>
       </c>
       <c r="R5" t="n">
-        <v>7054681</v>
+        <v>7054409</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,14 +1183,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,26 +1210,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1212,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124232343</v>
+        <v>124238954</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,42 +1243,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466050</v>
+        <v>466048</v>
       </c>
       <c r="R6" t="n">
-        <v>7054470</v>
+        <v>7054406</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,7 +1302,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1302,12 +1312,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1336,12 +1341,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1359,10 +1364,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124235290</v>
+        <v>124232343</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1375,37 +1380,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466069</v>
+        <v>466050</v>
       </c>
       <c r="R7" t="n">
-        <v>7054731</v>
+        <v>7054470</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1434,7 +1444,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,7 +1454,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1473,12 +1488,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124231227</v>
+        <v>124233935</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,34 +1527,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466082</v>
+        <v>466049</v>
       </c>
       <c r="R8" t="n">
-        <v>7054428</v>
+        <v>7054622</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1571,7 +1591,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1581,7 +1601,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1610,12 +1635,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1633,7 +1658,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124234661</v>
+        <v>124233251</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1673,10 +1698,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466088</v>
+        <v>466029</v>
       </c>
       <c r="R9" t="n">
-        <v>7054654</v>
+        <v>7054550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1708,7 +1733,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1718,7 +1743,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1770,10 +1795,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124238072</v>
+        <v>124235016</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1786,37 +1811,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466028</v>
+        <v>466066</v>
       </c>
       <c r="R10" t="n">
-        <v>7054700</v>
+        <v>7054677</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1845,7 +1875,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1855,7 +1885,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1884,12 +1919,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1907,7 +1942,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124235507</v>
+        <v>124237831</v>
       </c>
       <c r="B11" t="n">
         <v>91030</v>
@@ -1948,17 +1983,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466047</v>
+        <v>466048</v>
       </c>
       <c r="R11" t="n">
-        <v>7054739</v>
+        <v>7054795</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1987,7 +2022,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1997,7 +2032,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2026,12 +2061,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,10 +2084,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124233935</v>
+        <v>124231450</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2065,27 +2100,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2094,13 +2143,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466049</v>
+        <v>466113</v>
       </c>
       <c r="R12" t="n">
-        <v>7054622</v>
+        <v>7054408</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2129,7 +2178,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2139,12 +2188,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2159,26 +2208,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2196,7 +2225,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124233251</v>
+        <v>124237519</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2236,13 +2265,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466029</v>
+        <v>466024</v>
       </c>
       <c r="R13" t="n">
-        <v>7054550</v>
+        <v>7054752</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2271,7 +2300,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2281,7 +2310,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2298,16 +2327,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2315,7 +2334,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2333,10 +2352,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124229492</v>
+        <v>124233387</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2349,37 +2368,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466104</v>
+        <v>466025</v>
       </c>
       <c r="R14" t="n">
-        <v>7054370</v>
+        <v>7054632</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2408,7 +2432,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2418,7 +2442,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2447,12 +2471,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2470,10 +2494,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124229168</v>
+        <v>124235851</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2482,60 +2506,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466061</v>
+        <v>466040</v>
       </c>
       <c r="R15" t="n">
-        <v>7054409</v>
+        <v>7054923</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2564,7 +2569,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2574,7 +2579,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2589,6 +2594,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2606,10 +2631,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124231450</v>
+        <v>124235081</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2622,41 +2647,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2665,13 +2676,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466113</v>
+        <v>466058</v>
       </c>
       <c r="R16" t="n">
-        <v>7054408</v>
+        <v>7054681</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2698,24 +2709,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2730,6 +2731,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2747,10 +2768,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124238716</v>
+        <v>124230947</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2759,41 +2780,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466019</v>
+        <v>466100</v>
       </c>
       <c r="R17" t="n">
-        <v>7054567</v>
+        <v>7054439</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2822,7 +2857,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2832,7 +2867,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2847,26 +2882,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2884,7 +2899,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124235851</v>
+        <v>124236910</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2924,13 +2939,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466040</v>
+        <v>466024</v>
       </c>
       <c r="R18" t="n">
-        <v>7054923</v>
+        <v>7054965</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2959,7 +2974,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2969,7 +2984,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3021,7 +3036,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124233335</v>
+        <v>124236835</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -3057,17 +3072,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466029</v>
+        <v>466084</v>
       </c>
       <c r="R19" t="n">
-        <v>7054621</v>
+        <v>7054927</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3096,7 +3111,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3106,7 +3121,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3158,10 +3173,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124235016</v>
+        <v>124238072</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3174,42 +3189,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466066</v>
+        <v>466028</v>
       </c>
       <c r="R20" t="n">
-        <v>7054677</v>
+        <v>7054700</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3238,7 +3248,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3248,12 +3258,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3282,12 +3287,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3305,10 +3310,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124236594</v>
+        <v>124233335</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3317,60 +3322,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466108</v>
+        <v>466029</v>
       </c>
       <c r="R21" t="n">
-        <v>7054934</v>
+        <v>7054621</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3399,7 +3385,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3409,7 +3395,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3424,6 +3410,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3441,7 +3447,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124238954</v>
+        <v>124238716</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3481,13 +3487,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466048</v>
+        <v>466019</v>
       </c>
       <c r="R22" t="n">
-        <v>7054406</v>
+        <v>7054567</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3516,7 +3522,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3526,7 +3532,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3578,7 +3584,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124236835</v>
+        <v>124234661</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3614,17 +3620,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466084</v>
+        <v>466088</v>
       </c>
       <c r="R23" t="n">
-        <v>7054927</v>
+        <v>7054654</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3653,7 +3659,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3663,7 +3669,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3715,7 +3721,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124237831</v>
+        <v>124234049</v>
       </c>
       <c r="B24" t="n">
         <v>91030</v>
@@ -3756,17 +3762,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466048</v>
+        <v>466057</v>
       </c>
       <c r="R24" t="n">
-        <v>7054795</v>
+        <v>7054600</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3795,7 +3801,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3805,7 +3811,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3857,7 +3863,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124236910</v>
+        <v>124231227</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3893,17 +3899,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466024</v>
+        <v>466082</v>
       </c>
       <c r="R25" t="n">
-        <v>7054965</v>
+        <v>7054428</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3932,7 +3938,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3942,7 +3948,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4141,10 +4147,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124236542</v>
+        <v>124236594</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4153,41 +4159,60 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466114</v>
+        <v>466108</v>
       </c>
       <c r="R27" t="n">
-        <v>7054930</v>
+        <v>7054934</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4216,7 +4241,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4226,7 +4251,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4241,26 +4266,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4278,10 +4283,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124234435</v>
+        <v>124236233</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4294,42 +4299,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466046</v>
+        <v>466113</v>
       </c>
       <c r="R28" t="n">
-        <v>7054578</v>
+        <v>7054849</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124236233</v>
+        <v>124235290</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -4456,17 +4456,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466113</v>
+        <v>466069</v>
       </c>
       <c r="R29" t="n">
-        <v>7054849</v>
+        <v>7054731</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124234049</v>
+        <v>124235507</v>
       </c>
       <c r="B30" t="n">
         <v>91030</v>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466057</v>
+        <v>466047</v>
       </c>
       <c r="R30" t="n">
-        <v>7054600</v>
+        <v>7054739</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124230274</v>
+        <v>124233675</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4744,13 +4744,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466120</v>
+        <v>466039</v>
       </c>
       <c r="R31" t="n">
-        <v>7054456</v>
+        <v>7054631</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4846,7 +4846,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124233675</v>
+        <v>124230274</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4891,13 +4891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466039</v>
+        <v>466120</v>
       </c>
       <c r="R32" t="n">
-        <v>7054631</v>
+        <v>7054456</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124231714</v>
+        <v>124231120</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5009,27 +5009,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5038,13 +5038,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466077</v>
+        <v>466086</v>
       </c>
       <c r="R33" t="n">
-        <v>7054405</v>
+        <v>7054427</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5083,7 +5083,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5135,7 +5140,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124232050</v>
+        <v>124228589</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5171,12 +5176,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5185,13 +5185,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466045</v>
+        <v>466066</v>
       </c>
       <c r="R34" t="n">
-        <v>7054447</v>
+        <v>7054389</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5287,7 +5287,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124228749</v>
+        <v>124232609</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5321,24 +5321,31 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466066</v>
+        <v>466085</v>
       </c>
       <c r="R35" t="n">
-        <v>7054397</v>
+        <v>7054527</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5367,7 +5374,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5377,12 +5384,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5434,7 +5441,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124232609</v>
+        <v>124237622</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5468,28 +5475,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466085</v>
+        <v>466053</v>
       </c>
       <c r="R36" t="n">
-        <v>7054527</v>
+        <v>7054770</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5588,7 +5588,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124237622</v>
+        <v>124232959</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5627,19 +5627,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466053</v>
+        <v>466071</v>
       </c>
       <c r="R37" t="n">
-        <v>7054770</v>
+        <v>7054484</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5668,7 +5673,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5678,12 +5683,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5735,7 +5740,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124237940</v>
+        <v>124228388</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5771,27 +5776,22 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466040</v>
+        <v>466017</v>
       </c>
       <c r="R38" t="n">
-        <v>7054768</v>
+        <v>7054386</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5887,7 +5887,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124236498</v>
+        <v>124232050</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5923,22 +5923,27 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466123</v>
+        <v>466045</v>
       </c>
       <c r="R39" t="n">
-        <v>7054939</v>
+        <v>7054447</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5967,7 +5972,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5977,12 +5982,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6034,10 +6039,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124229096</v>
+        <v>124231714</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6050,45 +6055,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466061</v>
+        <v>466077</v>
       </c>
       <c r="R40" t="n">
-        <v>7054411</v>
+        <v>7054405</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6117,7 +6119,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6127,12 +6129,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6184,10 +6181,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124233428</v>
+        <v>124237940</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6200,16 +6197,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6223,19 +6220,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466026</v>
+        <v>466040</v>
       </c>
       <c r="R41" t="n">
-        <v>7054647</v>
+        <v>7054768</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6264,7 +6266,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6274,12 +6276,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6331,10 +6333,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124231120</v>
+        <v>124233428</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6347,16 +6349,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6367,7 +6369,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6376,13 +6378,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466086</v>
+        <v>466026</v>
       </c>
       <c r="R42" t="n">
-        <v>7054427</v>
+        <v>7054647</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6411,7 +6413,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6421,12 +6423,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6478,7 +6480,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124228388</v>
+        <v>124236498</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6519,17 +6521,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466017</v>
+        <v>466123</v>
       </c>
       <c r="R43" t="n">
-        <v>7054386</v>
+        <v>7054939</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6558,7 +6560,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6568,12 +6570,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6625,7 +6627,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124235393</v>
+        <v>124228749</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6661,7 +6663,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6670,13 +6672,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466051</v>
+        <v>466066</v>
       </c>
       <c r="R44" t="n">
-        <v>7054737</v>
+        <v>7054397</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6705,7 +6707,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6715,12 +6717,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6772,7 +6774,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124228589</v>
+        <v>124235393</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6817,13 +6819,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466066</v>
+        <v>466051</v>
       </c>
       <c r="R45" t="n">
-        <v>7054389</v>
+        <v>7054737</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6852,7 +6854,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6862,7 +6864,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6919,7 +6921,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124232959</v>
+        <v>124229096</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6953,26 +6955,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466071</v>
+        <v>466061</v>
       </c>
       <c r="R46" t="n">
-        <v>7054484</v>
+        <v>7054411</v>
       </c>
       <c r="S46" t="n">
         <v>12</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124236542</v>
+        <v>124235016</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466114</v>
+        <v>466066</v>
       </c>
       <c r="R2" t="n">
-        <v>7054930</v>
+        <v>7054677</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124234435</v>
+        <v>124229168</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,31 +834,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,13 +881,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466046</v>
+        <v>466061</v>
       </c>
       <c r="R3" t="n">
-        <v>7054578</v>
+        <v>7054409</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +916,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +926,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,26 +941,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +958,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124229492</v>
+        <v>124234435</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,34 +974,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466104</v>
+        <v>466046</v>
       </c>
       <c r="R4" t="n">
-        <v>7054370</v>
+        <v>7054578</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1029,7 +1038,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1048,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,12 +1077,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1091,10 +1100,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124229168</v>
+        <v>124231227</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,60 +1112,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466061</v>
+        <v>466082</v>
       </c>
       <c r="R5" t="n">
-        <v>7054409</v>
+        <v>7054428</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1185,7 +1175,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1185,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,6 +1200,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1227,7 +1237,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124238954</v>
+        <v>124238716</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1267,13 +1277,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466048</v>
+        <v>466019</v>
       </c>
       <c r="R6" t="n">
-        <v>7054406</v>
+        <v>7054567</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1302,7 +1312,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1312,7 +1322,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1364,7 +1374,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124232343</v>
+        <v>124233387</v>
       </c>
       <c r="B7" t="n">
         <v>91030</v>
@@ -1409,13 +1419,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466050</v>
+        <v>466025</v>
       </c>
       <c r="R7" t="n">
-        <v>7054470</v>
+        <v>7054632</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1444,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1454,12 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1488,12 +1493,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124233935</v>
+        <v>124233251</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1527,42 +1532,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466049</v>
+        <v>466029</v>
       </c>
       <c r="R8" t="n">
-        <v>7054622</v>
+        <v>7054550</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1601,12 +1601,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1635,12 +1630,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124233251</v>
+        <v>124234049</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1674,37 +1669,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466029</v>
+        <v>466057</v>
       </c>
       <c r="R9" t="n">
-        <v>7054550</v>
+        <v>7054600</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124235016</v>
+        <v>124237831</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1811,42 +1811,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466066</v>
+        <v>466048</v>
       </c>
       <c r="R10" t="n">
-        <v>7054677</v>
+        <v>7054795</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1885,12 +1885,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1942,10 +1937,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124237831</v>
+        <v>124235290</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1958,42 +1953,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466048</v>
+        <v>466069</v>
       </c>
       <c r="R11" t="n">
-        <v>7054795</v>
+        <v>7054731</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2022,7 +2012,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2032,7 +2022,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2061,12 +2051,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2084,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124231450</v>
+        <v>124230947</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2096,25 +2086,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2132,21 +2122,16 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466113</v>
+        <v>466100</v>
       </c>
       <c r="R12" t="n">
-        <v>7054408</v>
+        <v>7054439</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2178,7 +2163,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2188,12 +2173,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2225,10 +2205,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124237519</v>
+        <v>124235507</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2241,37 +2221,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466024</v>
+        <v>466047</v>
       </c>
       <c r="R13" t="n">
-        <v>7054752</v>
+        <v>7054739</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2300,7 +2285,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2310,7 +2295,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2327,14 +2312,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124233387</v>
+        <v>124236835</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2368,42 +2363,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466025</v>
+        <v>466084</v>
       </c>
       <c r="R14" t="n">
-        <v>7054632</v>
+        <v>7054927</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2432,7 +2422,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2442,7 +2432,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2471,12 +2461,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2494,10 +2484,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124235851</v>
+        <v>124238409</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2510,37 +2500,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466040</v>
+        <v>466019</v>
       </c>
       <c r="R15" t="n">
-        <v>7054923</v>
+        <v>7054696</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2579,7 +2574,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124235081</v>
+        <v>124238954</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2647,42 +2647,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466058</v>
+        <v>466048</v>
       </c>
       <c r="R16" t="n">
-        <v>7054681</v>
+        <v>7054406</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2709,14 +2704,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124230947</v>
+        <v>124236542</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2780,55 +2780,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466100</v>
+        <v>466114</v>
       </c>
       <c r="R17" t="n">
-        <v>7054439</v>
+        <v>7054930</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2857,7 +2843,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2867,7 +2853,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2882,6 +2868,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2899,7 +2905,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124236910</v>
+        <v>124235851</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2939,13 +2945,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466024</v>
+        <v>466040</v>
       </c>
       <c r="R18" t="n">
-        <v>7054965</v>
+        <v>7054923</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2974,7 +2980,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2984,7 +2990,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3036,10 +3042,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124236835</v>
+        <v>124232343</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3052,34 +3058,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466084</v>
+        <v>466050</v>
       </c>
       <c r="R19" t="n">
-        <v>7054927</v>
+        <v>7054470</v>
       </c>
       <c r="S19" t="n">
         <v>11</v>
@@ -3111,7 +3122,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3121,7 +3132,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3150,12 +3166,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3173,7 +3189,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124238072</v>
+        <v>124237519</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -3213,13 +3229,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466028</v>
+        <v>466024</v>
       </c>
       <c r="R20" t="n">
-        <v>7054700</v>
+        <v>7054752</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3248,7 +3264,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3258,7 +3274,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3275,16 +3291,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM20" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3292,7 +3298,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3310,10 +3316,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124233335</v>
+        <v>124231450</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3326,37 +3332,56 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466029</v>
+        <v>466113</v>
       </c>
       <c r="R21" t="n">
-        <v>7054621</v>
+        <v>7054408</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3385,7 +3410,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3395,7 +3420,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3410,26 +3440,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3447,10 +3457,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124238716</v>
+        <v>124236594</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3459,38 +3469,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466019</v>
+        <v>466108</v>
       </c>
       <c r="R22" t="n">
-        <v>7054567</v>
+        <v>7054934</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3522,7 +3551,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3532,7 +3561,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3547,26 +3576,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3584,7 +3593,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124234661</v>
+        <v>124236233</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3620,14 +3629,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466088</v>
+        <v>466113</v>
       </c>
       <c r="R23" t="n">
-        <v>7054654</v>
+        <v>7054849</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3659,7 +3668,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3669,7 +3678,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3683,7 +3692,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3721,7 +3730,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124234049</v>
+        <v>124235081</v>
       </c>
       <c r="B24" t="n">
         <v>91030</v>
@@ -3766,13 +3775,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466057</v>
+        <v>466058</v>
       </c>
       <c r="R24" t="n">
-        <v>7054600</v>
+        <v>7054681</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3799,19 +3808,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:58</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3863,7 +3867,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124231227</v>
+        <v>124229492</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3903,13 +3907,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466082</v>
+        <v>466104</v>
       </c>
       <c r="R25" t="n">
-        <v>7054428</v>
+        <v>7054370</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3938,7 +3942,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3948,7 +3952,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4000,10 +4004,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124238409</v>
+        <v>124233935</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4016,27 +4020,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4045,13 +4049,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466019</v>
+        <v>466049</v>
       </c>
       <c r="R26" t="n">
-        <v>7054696</v>
+        <v>7054622</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4080,7 +4084,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4090,12 +4094,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4124,12 +4128,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4147,10 +4151,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124236594</v>
+        <v>124236910</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4159,57 +4163,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466108</v>
+        <v>466024</v>
       </c>
       <c r="R27" t="n">
-        <v>7054934</v>
+        <v>7054965</v>
       </c>
       <c r="S27" t="n">
         <v>8</v>
@@ -4241,7 +4226,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4251,7 +4236,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4266,6 +4251,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4283,7 +4288,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124236233</v>
+        <v>124238072</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -4319,17 +4324,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466113</v>
+        <v>466028</v>
       </c>
       <c r="R28" t="n">
-        <v>7054849</v>
+        <v>7054700</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4368,7 +4373,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4382,7 +4387,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4420,7 +4425,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124235290</v>
+        <v>124234661</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -4460,13 +4465,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466069</v>
+        <v>466088</v>
       </c>
       <c r="R29" t="n">
-        <v>7054731</v>
+        <v>7054654</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4495,7 +4500,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4505,7 +4510,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4534,12 +4539,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4557,10 +4562,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124235507</v>
+        <v>124233335</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4573,42 +4578,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466047</v>
+        <v>466029</v>
       </c>
       <c r="R30" t="n">
-        <v>7054739</v>
+        <v>7054621</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124233675</v>
+        <v>124231714</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4715,27 +4715,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4744,13 +4744,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466039</v>
+        <v>466077</v>
       </c>
       <c r="R31" t="n">
-        <v>7054631</v>
+        <v>7054405</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4789,12 +4789,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4846,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124230274</v>
+        <v>124229096</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4880,24 +4875,27 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466120</v>
+        <v>466061</v>
       </c>
       <c r="R32" t="n">
-        <v>7054456</v>
+        <v>7054411</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4926,7 +4924,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4936,12 +4934,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4993,7 +4991,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124231120</v>
+        <v>124232050</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5029,7 +5027,12 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5038,13 +5041,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466086</v>
+        <v>466045</v>
       </c>
       <c r="R33" t="n">
-        <v>7054427</v>
+        <v>7054447</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5073,7 +5076,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5083,12 +5086,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5140,7 +5143,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124228589</v>
+        <v>124236498</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5181,17 +5184,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466066</v>
+        <v>466123</v>
       </c>
       <c r="R34" t="n">
-        <v>7054389</v>
+        <v>7054939</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5220,7 +5223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5230,12 +5233,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5441,7 +5444,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124237622</v>
+        <v>124231120</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5482,17 +5485,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466053</v>
+        <v>466086</v>
       </c>
       <c r="R36" t="n">
-        <v>7054770</v>
+        <v>7054427</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5521,7 +5524,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5531,12 +5534,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5588,7 +5591,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124232959</v>
+        <v>124237940</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5624,7 +5627,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5634,17 +5637,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466071</v>
+        <v>466040</v>
       </c>
       <c r="R37" t="n">
-        <v>7054484</v>
+        <v>7054768</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5673,7 +5676,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5683,12 +5686,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5740,7 +5743,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124228388</v>
+        <v>124233675</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5776,7 +5779,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5785,13 +5788,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466017</v>
+        <v>466039</v>
       </c>
       <c r="R38" t="n">
-        <v>7054386</v>
+        <v>7054631</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5820,7 +5823,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5830,12 +5833,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5887,7 +5890,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124232050</v>
+        <v>124237622</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5923,27 +5926,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466045</v>
+        <v>466053</v>
       </c>
       <c r="R39" t="n">
-        <v>7054447</v>
+        <v>7054770</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5972,7 +5970,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5982,12 +5980,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6039,10 +6037,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124231714</v>
+        <v>124228589</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6055,27 +6053,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6084,13 +6082,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466077</v>
+        <v>466066</v>
       </c>
       <c r="R40" t="n">
-        <v>7054405</v>
+        <v>7054389</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6119,7 +6117,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6129,7 +6127,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6181,7 +6184,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124237940</v>
+        <v>124230274</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6220,24 +6223,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466040</v>
+        <v>466120</v>
       </c>
       <c r="R41" t="n">
-        <v>7054768</v>
+        <v>7054456</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6266,7 +6264,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6276,12 +6274,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6333,10 +6331,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124233428</v>
+        <v>124228749</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6349,16 +6347,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6378,13 +6376,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466026</v>
+        <v>466066</v>
       </c>
       <c r="R42" t="n">
-        <v>7054647</v>
+        <v>7054397</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6413,7 +6411,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6423,12 +6421,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6480,7 +6478,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124236498</v>
+        <v>124228388</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6521,17 +6519,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466123</v>
+        <v>466017</v>
       </c>
       <c r="R43" t="n">
-        <v>7054939</v>
+        <v>7054386</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6560,7 +6558,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6570,12 +6568,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6627,7 +6625,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124228749</v>
+        <v>124232959</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6663,7 +6661,12 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6672,13 +6675,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466066</v>
+        <v>466071</v>
       </c>
       <c r="R44" t="n">
-        <v>7054397</v>
+        <v>7054484</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6707,7 +6710,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6717,12 +6720,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6774,10 +6777,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124235393</v>
+        <v>124233428</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6790,16 +6793,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6810,7 +6813,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6819,10 +6822,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466051</v>
+        <v>466026</v>
       </c>
       <c r="R45" t="n">
-        <v>7054737</v>
+        <v>7054647</v>
       </c>
       <c r="S45" t="n">
         <v>11</v>
@@ -6854,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6864,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6921,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124229096</v>
+        <v>124235393</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6955,27 +6958,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466061</v>
+        <v>466051</v>
       </c>
       <c r="R46" t="n">
-        <v>7054411</v>
+        <v>7054737</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -822,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124229168</v>
+        <v>124234435</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,45 +834,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -881,13 +867,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466061</v>
+        <v>466046</v>
       </c>
       <c r="R3" t="n">
-        <v>7054409</v>
+        <v>7054578</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -926,7 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,6 +927,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -958,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124234435</v>
+        <v>124231227</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,42 +980,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466046</v>
+        <v>466082</v>
       </c>
       <c r="R4" t="n">
-        <v>7054578</v>
+        <v>7054428</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1048,7 +1049,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,12 +1078,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1100,10 +1101,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124231227</v>
+        <v>124229168</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,41 +1113,60 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466082</v>
+        <v>466061</v>
       </c>
       <c r="R5" t="n">
-        <v>7054428</v>
+        <v>7054409</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1175,7 +1195,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1185,7 +1205,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,26 +1220,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124231714</v>
+        <v>124229096</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4715,42 +4715,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466077</v>
+        <v>466061</v>
       </c>
       <c r="R31" t="n">
-        <v>7054405</v>
+        <v>7054411</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4779,7 +4782,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4789,7 +4792,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4841,10 +4849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124229096</v>
+        <v>124231714</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4857,45 +4865,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466061</v>
+        <v>466077</v>
       </c>
       <c r="R32" t="n">
-        <v>7054411</v>
+        <v>7054405</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4924,7 +4929,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4934,12 +4939,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124235016</v>
+        <v>124235081</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466066</v>
+        <v>466058</v>
       </c>
       <c r="R2" t="n">
-        <v>7054677</v>
+        <v>7054681</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,24 +753,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -822,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124234435</v>
+        <v>124238409</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,27 +828,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -867,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466046</v>
+        <v>466019</v>
       </c>
       <c r="R3" t="n">
-        <v>7054578</v>
+        <v>7054696</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -964,7 +959,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124231227</v>
+        <v>124236910</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -1000,17 +995,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466082</v>
+        <v>466024</v>
       </c>
       <c r="R4" t="n">
-        <v>7054428</v>
+        <v>7054965</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,7 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1101,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124229168</v>
+        <v>124235851</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1113,60 +1108,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466061</v>
+        <v>466040</v>
       </c>
       <c r="R5" t="n">
-        <v>7054409</v>
+        <v>7054923</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1195,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1205,7 +1181,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,6 +1196,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,10 +1233,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124238716</v>
+        <v>124231450</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,37 +1249,56 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466019</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>7054567</v>
+        <v>7054408</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1312,7 +1327,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1322,7 +1337,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1337,26 +1357,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124233387</v>
+        <v>124238072</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1390,42 +1390,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466025</v>
+        <v>466028</v>
       </c>
       <c r="R7" t="n">
-        <v>7054632</v>
+        <v>7054700</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1454,7 +1449,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1459,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1493,12 +1488,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1516,7 +1511,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124233251</v>
+        <v>124236542</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1552,17 +1547,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466029</v>
+        <v>466114</v>
       </c>
       <c r="R8" t="n">
-        <v>7054550</v>
+        <v>7054930</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1591,7 +1586,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1601,7 +1596,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1795,7 +1790,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124237831</v>
+        <v>124235507</v>
       </c>
       <c r="B10" t="n">
         <v>91030</v>
@@ -1836,17 +1831,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466048</v>
+        <v>466047</v>
       </c>
       <c r="R10" t="n">
-        <v>7054795</v>
+        <v>7054739</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1914,12 +1909,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1937,10 +1932,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124235290</v>
+        <v>124229168</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1949,41 +1944,60 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466069</v>
+        <v>466061</v>
       </c>
       <c r="R11" t="n">
-        <v>7054731</v>
+        <v>7054409</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2012,7 +2026,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2022,7 +2036,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2037,26 +2051,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2074,10 +2068,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230947</v>
+        <v>124236233</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2086,55 +2080,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466100</v>
+        <v>466113</v>
       </c>
       <c r="R12" t="n">
-        <v>7054439</v>
+        <v>7054849</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2163,7 +2143,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2173,7 +2153,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2187,7 +2167,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124235507</v>
+        <v>124237519</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2221,42 +2221,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466047</v>
+        <v>466024</v>
       </c>
       <c r="R13" t="n">
-        <v>7054739</v>
+        <v>7054752</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2285,7 +2280,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2295,7 +2290,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2312,24 +2307,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2347,10 +2332,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124236835</v>
+        <v>124237831</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2363,37 +2348,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466084</v>
+        <v>466048</v>
       </c>
       <c r="R14" t="n">
-        <v>7054927</v>
+        <v>7054795</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2422,7 +2412,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2432,7 +2422,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2461,12 +2451,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2484,10 +2474,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124238409</v>
+        <v>124233387</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2500,27 +2490,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2529,13 +2519,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466019</v>
+        <v>466025</v>
       </c>
       <c r="R15" t="n">
-        <v>7054696</v>
+        <v>7054632</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2564,7 +2554,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2574,12 +2564,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,12 +2593,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2631,7 +2616,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124238954</v>
+        <v>124233251</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2671,13 +2656,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466048</v>
+        <v>466029</v>
       </c>
       <c r="R16" t="n">
-        <v>7054406</v>
+        <v>7054550</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2706,7 +2691,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2716,7 +2701,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2768,10 +2753,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124236542</v>
+        <v>124234435</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2784,37 +2769,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466114</v>
+        <v>466046</v>
       </c>
       <c r="R17" t="n">
-        <v>7054930</v>
+        <v>7054578</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2843,7 +2833,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2853,7 +2843,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2882,12 +2872,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2905,10 +2895,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124235851</v>
+        <v>124232343</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2921,34 +2911,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466040</v>
+        <v>466050</v>
       </c>
       <c r="R18" t="n">
-        <v>7054923</v>
+        <v>7054470</v>
       </c>
       <c r="S18" t="n">
         <v>11</v>
@@ -2980,7 +2975,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2990,7 +2985,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124232343</v>
+        <v>124235016</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3058,27 +3058,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466050</v>
+        <v>466066</v>
       </c>
       <c r="R19" t="n">
-        <v>7054470</v>
+        <v>7054677</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3189,7 +3189,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124237519</v>
+        <v>124238716</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466024</v>
+        <v>466019</v>
       </c>
       <c r="R20" t="n">
-        <v>7054752</v>
+        <v>7054567</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3291,6 +3291,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM20" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3298,7 +3308,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3316,10 +3326,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124231450</v>
+        <v>124233935</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3332,41 +3342,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3375,13 +3371,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466113</v>
+        <v>466049</v>
       </c>
       <c r="R21" t="n">
-        <v>7054408</v>
+        <v>7054622</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3410,7 +3406,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3420,12 +3416,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3440,6 +3436,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3457,10 +3473,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124236594</v>
+        <v>124236835</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3469,60 +3485,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466108</v>
+        <v>466084</v>
       </c>
       <c r="R22" t="n">
-        <v>7054934</v>
+        <v>7054927</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3551,7 +3548,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3561,7 +3558,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3576,6 +3573,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3593,7 +3610,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124236233</v>
+        <v>124238954</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3629,17 +3646,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466113</v>
+        <v>466048</v>
       </c>
       <c r="R23" t="n">
-        <v>7054849</v>
+        <v>7054406</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3668,7 +3685,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3678,7 +3695,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3692,7 +3709,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3730,10 +3747,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124235081</v>
+        <v>124235290</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3746,42 +3763,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466058</v>
+        <v>466069</v>
       </c>
       <c r="R24" t="n">
-        <v>7054681</v>
+        <v>7054731</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3808,14 +3820,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3844,12 +3861,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3867,7 +3884,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124229492</v>
+        <v>124233335</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3907,13 +3924,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466104</v>
+        <v>466029</v>
       </c>
       <c r="R25" t="n">
-        <v>7054370</v>
+        <v>7054621</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3942,7 +3959,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3952,7 +3969,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4004,10 +4021,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124233935</v>
+        <v>124230947</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4016,31 +4033,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4049,13 +4075,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466049</v>
+        <v>466100</v>
       </c>
       <c r="R26" t="n">
-        <v>7054622</v>
+        <v>7054439</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4084,7 +4110,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4094,12 +4120,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4114,26 +4135,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4151,7 +4152,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124236910</v>
+        <v>124234661</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -4187,17 +4188,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466024</v>
+        <v>466088</v>
       </c>
       <c r="R27" t="n">
-        <v>7054965</v>
+        <v>7054654</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4226,7 +4227,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4236,7 +4237,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4288,7 +4289,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124238072</v>
+        <v>124231227</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -4328,13 +4329,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466028</v>
+        <v>466082</v>
       </c>
       <c r="R28" t="n">
-        <v>7054700</v>
+        <v>7054428</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4363,7 +4364,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4373,7 +4374,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4425,7 +4426,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124234661</v>
+        <v>124229492</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -4465,13 +4466,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466088</v>
+        <v>466104</v>
       </c>
       <c r="R29" t="n">
-        <v>7054654</v>
+        <v>7054370</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4500,7 +4501,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4510,7 +4511,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4562,10 +4563,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124233335</v>
+        <v>124236594</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4574,41 +4575,60 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466029</v>
+        <v>466108</v>
       </c>
       <c r="R30" t="n">
-        <v>7054621</v>
+        <v>7054934</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4637,7 +4657,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4647,7 +4667,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4662,26 +4682,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124229096</v>
+        <v>124232050</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4733,27 +4733,29 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466061</v>
+        <v>466045</v>
       </c>
       <c r="R31" t="n">
-        <v>7054411</v>
+        <v>7054447</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4782,7 +4784,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4792,12 +4794,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4991,7 +4993,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124232050</v>
+        <v>124228589</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5027,12 +5029,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5041,13 +5038,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466045</v>
+        <v>466066</v>
       </c>
       <c r="R33" t="n">
-        <v>7054447</v>
+        <v>7054389</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5076,7 +5073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5086,12 +5083,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5143,7 +5140,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124236498</v>
+        <v>124228749</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5179,22 +5176,22 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466123</v>
+        <v>466066</v>
       </c>
       <c r="R34" t="n">
-        <v>7054939</v>
+        <v>7054397</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5223,7 +5220,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5233,12 +5230,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5290,7 +5287,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124232609</v>
+        <v>124228388</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5324,16 +5321,9 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5342,13 +5332,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466085</v>
+        <v>466017</v>
       </c>
       <c r="R35" t="n">
-        <v>7054527</v>
+        <v>7054386</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5377,7 +5367,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5387,12 +5377,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5444,7 +5434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124231120</v>
+        <v>124233675</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5480,7 +5470,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5489,13 +5479,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466086</v>
+        <v>466039</v>
       </c>
       <c r="R36" t="n">
-        <v>7054427</v>
+        <v>7054631</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5524,7 +5514,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5534,12 +5524,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5591,7 +5581,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124237940</v>
+        <v>124229096</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5625,29 +5615,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466040</v>
+        <v>466061</v>
       </c>
       <c r="R37" t="n">
-        <v>7054768</v>
+        <v>7054411</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5676,7 +5664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5686,12 +5674,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5743,7 +5731,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124233675</v>
+        <v>124230274</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5788,13 +5776,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466039</v>
+        <v>466120</v>
       </c>
       <c r="R38" t="n">
-        <v>7054631</v>
+        <v>7054456</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5823,7 +5811,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5833,12 +5821,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5890,7 +5878,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124237622</v>
+        <v>124232959</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5929,19 +5917,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466053</v>
+        <v>466071</v>
       </c>
       <c r="R39" t="n">
-        <v>7054770</v>
+        <v>7054484</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5970,7 +5963,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5980,12 +5973,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6037,10 +6030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124228589</v>
+        <v>124233428</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6053,16 +6046,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6073,7 +6066,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6082,13 +6075,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466066</v>
+        <v>466026</v>
       </c>
       <c r="R40" t="n">
-        <v>7054389</v>
+        <v>7054647</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6117,7 +6110,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6127,12 +6120,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6184,7 +6177,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124230274</v>
+        <v>124235393</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6220,7 +6213,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6229,10 +6222,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466120</v>
+        <v>466051</v>
       </c>
       <c r="R41" t="n">
-        <v>7054456</v>
+        <v>7054737</v>
       </c>
       <c r="S41" t="n">
         <v>11</v>
@@ -6264,7 +6257,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6274,12 +6267,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6331,7 +6324,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124228749</v>
+        <v>124237940</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6370,19 +6363,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466066</v>
+        <v>466040</v>
       </c>
       <c r="R42" t="n">
-        <v>7054397</v>
+        <v>7054768</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6411,7 +6409,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6421,12 +6419,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6478,7 +6476,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124228388</v>
+        <v>124236498</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6519,17 +6517,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466017</v>
+        <v>466123</v>
       </c>
       <c r="R43" t="n">
-        <v>7054386</v>
+        <v>7054939</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6558,7 +6556,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6568,12 +6566,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6625,7 +6623,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124232959</v>
+        <v>124231120</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6664,24 +6662,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466071</v>
+        <v>466086</v>
       </c>
       <c r="R44" t="n">
-        <v>7054484</v>
+        <v>7054427</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6703,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6713,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6777,10 +6770,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124233428</v>
+        <v>124232609</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6793,16 +6786,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6811,24 +6804,31 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466026</v>
+        <v>466085</v>
       </c>
       <c r="R45" t="n">
-        <v>7054647</v>
+        <v>7054527</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124235393</v>
+        <v>124237622</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6965,17 +6965,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466051</v>
+        <v>466053</v>
       </c>
       <c r="R46" t="n">
-        <v>7054737</v>
+        <v>7054770</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -3610,10 +3610,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124238954</v>
+        <v>124230947</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3622,41 +3622,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466048</v>
+        <v>466100</v>
       </c>
       <c r="R23" t="n">
-        <v>7054406</v>
+        <v>7054439</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3685,7 +3699,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3695,7 +3709,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3710,26 +3724,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3747,7 +3741,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124235290</v>
+        <v>124238954</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3787,13 +3781,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466069</v>
+        <v>466048</v>
       </c>
       <c r="R24" t="n">
-        <v>7054731</v>
+        <v>7054406</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3822,7 +3816,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3832,7 +3826,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3861,12 +3855,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3884,7 +3878,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124233335</v>
+        <v>124235290</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3924,13 +3918,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466029</v>
+        <v>466069</v>
       </c>
       <c r="R25" t="n">
-        <v>7054621</v>
+        <v>7054731</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3959,7 +3953,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3969,7 +3963,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3998,12 +3992,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4021,10 +4015,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124230947</v>
+        <v>124233335</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4033,55 +4027,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466100</v>
+        <v>466029</v>
       </c>
       <c r="R26" t="n">
-        <v>7054439</v>
+        <v>7054621</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4110,7 +4090,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4120,7 +4100,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4135,6 +4115,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -2616,14 +2616,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124233251</v>
+        <v>124235016</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2632,37 +2632,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466029</v>
+        <v>466066</v>
       </c>
       <c r="R16" t="n">
-        <v>7054550</v>
+        <v>7054677</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2691,7 +2696,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2701,7 +2706,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2730,12 +2740,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2753,10 +2763,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124234435</v>
+        <v>124233251</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2769,42 +2779,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466046</v>
+        <v>466029</v>
       </c>
       <c r="R17" t="n">
-        <v>7054578</v>
+        <v>7054550</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2833,7 +2838,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2843,7 +2848,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2872,12 +2877,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2895,7 +2900,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124232343</v>
+        <v>124234435</v>
       </c>
       <c r="B18" t="n">
         <v>91030</v>
@@ -2940,13 +2945,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466050</v>
+        <v>466046</v>
       </c>
       <c r="R18" t="n">
-        <v>7054470</v>
+        <v>7054578</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2975,7 +2980,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2985,12 +2990,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124235016</v>
+        <v>124232343</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3058,27 +3058,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466066</v>
+        <v>466050</v>
       </c>
       <c r="R19" t="n">
-        <v>7054677</v>
+        <v>7054470</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3610,10 +3610,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124230947</v>
+        <v>124238954</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3622,55 +3622,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466100</v>
+        <v>466048</v>
       </c>
       <c r="R23" t="n">
-        <v>7054439</v>
+        <v>7054406</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3699,7 +3685,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3709,7 +3695,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3724,6 +3710,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3741,7 +3747,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124238954</v>
+        <v>124235290</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3781,13 +3787,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466048</v>
+        <v>466069</v>
       </c>
       <c r="R24" t="n">
-        <v>7054406</v>
+        <v>7054731</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3816,7 +3822,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3826,7 +3832,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3855,12 +3861,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3878,7 +3884,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124235290</v>
+        <v>124233335</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3918,13 +3924,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466069</v>
+        <v>466029</v>
       </c>
       <c r="R25" t="n">
-        <v>7054731</v>
+        <v>7054621</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3953,7 +3959,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3963,7 +3969,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3992,12 +3998,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4015,10 +4021,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124233335</v>
+        <v>124230947</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4027,41 +4033,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466029</v>
+        <v>466100</v>
       </c>
       <c r="R26" t="n">
-        <v>7054621</v>
+        <v>7054439</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4090,7 +4110,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4100,7 +4120,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4115,26 +4135,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124235081</v>
+        <v>124229168</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466058</v>
+        <v>466061</v>
       </c>
       <c r="R2" t="n">
-        <v>7054681</v>
+        <v>7054409</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,14 +767,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,26 +794,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124238409</v>
+        <v>124235507</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,27 +827,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466019</v>
+        <v>466047</v>
       </c>
       <c r="R3" t="n">
-        <v>7054696</v>
+        <v>7054739</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -892,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +901,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -959,7 +953,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124236910</v>
+        <v>124233335</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -995,17 +989,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466024</v>
+        <v>466029</v>
       </c>
       <c r="R4" t="n">
-        <v>7054965</v>
+        <v>7054621</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1028,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1038,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1096,10 +1090,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124235851</v>
+        <v>124237831</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,37 +1106,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466040</v>
+        <v>466048</v>
       </c>
       <c r="R5" t="n">
-        <v>7054923</v>
+        <v>7054795</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1171,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,7 +1180,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,12 +1209,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1233,10 +1232,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124231450</v>
+        <v>124236594</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,25 +1244,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1288,17 +1287,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466113</v>
+        <v>466108</v>
       </c>
       <c r="R6" t="n">
-        <v>7054408</v>
+        <v>7054934</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1327,7 +1326,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1337,12 +1336,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1374,7 +1368,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124238072</v>
+        <v>124236835</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1410,14 +1404,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466028</v>
+        <v>466084</v>
       </c>
       <c r="R7" t="n">
-        <v>7054700</v>
+        <v>7054927</v>
       </c>
       <c r="S7" t="n">
         <v>11</v>
@@ -1449,7 +1443,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1459,7 +1453,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1511,7 +1505,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124236542</v>
+        <v>124235290</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1547,17 +1541,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466114</v>
+        <v>466069</v>
       </c>
       <c r="R8" t="n">
-        <v>7054930</v>
+        <v>7054731</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1586,7 +1580,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1596,7 +1590,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1625,12 +1619,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1648,10 +1642,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124234049</v>
+        <v>124229492</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,42 +1658,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466057</v>
+        <v>466104</v>
       </c>
       <c r="R9" t="n">
-        <v>7054600</v>
+        <v>7054370</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1728,7 +1717,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,7 +1727,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1767,12 +1756,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1790,10 +1779,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124235507</v>
+        <v>124234661</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1806,42 +1795,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466047</v>
+        <v>466088</v>
       </c>
       <c r="R10" t="n">
-        <v>7054739</v>
+        <v>7054654</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1870,7 +1854,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1880,7 +1864,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1909,12 +1893,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1932,10 +1916,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124229168</v>
+        <v>124238409</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1944,20 +1928,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1965,24 +1949,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1991,13 +1961,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466061</v>
+        <v>466019</v>
       </c>
       <c r="R11" t="n">
-        <v>7054409</v>
+        <v>7054696</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2026,7 +1996,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2036,7 +2006,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2051,6 +2026,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2068,10 +2063,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124236233</v>
+        <v>124234049</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2084,37 +2079,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466113</v>
+        <v>466057</v>
       </c>
       <c r="R12" t="n">
-        <v>7054849</v>
+        <v>7054600</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124237519</v>
+        <v>124230947</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2217,41 +2217,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466024</v>
+        <v>466100</v>
       </c>
       <c r="R13" t="n">
-        <v>7054752</v>
+        <v>7054439</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2280,7 +2294,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2290,7 +2304,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2305,16 +2319,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2332,10 +2336,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124237831</v>
+        <v>124235851</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2348,42 +2352,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466048</v>
+        <v>466040</v>
       </c>
       <c r="R14" t="n">
-        <v>7054795</v>
+        <v>7054923</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2412,7 +2411,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2422,7 +2421,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2451,12 +2450,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2474,10 +2473,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124233387</v>
+        <v>124231450</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2490,27 +2489,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2519,13 +2532,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466025</v>
+        <v>466113</v>
       </c>
       <c r="R15" t="n">
-        <v>7054632</v>
+        <v>7054408</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2554,7 +2567,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2564,7 +2577,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2579,26 +2597,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2616,14 +2614,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124235016</v>
+        <v>124233251</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2632,42 +2630,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466066</v>
+        <v>466029</v>
       </c>
       <c r="R16" t="n">
-        <v>7054677</v>
+        <v>7054550</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2696,7 +2689,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2706,12 +2699,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2740,12 +2728,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2763,7 +2751,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124233251</v>
+        <v>124238954</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2803,13 +2791,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466029</v>
+        <v>466048</v>
       </c>
       <c r="R17" t="n">
-        <v>7054550</v>
+        <v>7054406</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2838,7 +2826,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2848,7 +2836,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2900,7 +2888,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124234435</v>
+        <v>124232343</v>
       </c>
       <c r="B18" t="n">
         <v>91030</v>
@@ -2945,13 +2933,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466046</v>
+        <v>466050</v>
       </c>
       <c r="R18" t="n">
-        <v>7054578</v>
+        <v>7054470</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2980,7 +2968,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2990,7 +2978,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3019,12 +3012,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3042,10 +3035,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124232343</v>
+        <v>124231227</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3058,42 +3051,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466050</v>
+        <v>466082</v>
       </c>
       <c r="R19" t="n">
-        <v>7054470</v>
+        <v>7054428</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3122,7 +3110,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3132,12 +3120,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3166,12 +3149,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3189,7 +3172,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124238716</v>
+        <v>124236910</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -3225,14 +3208,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466019</v>
+        <v>466024</v>
       </c>
       <c r="R20" t="n">
-        <v>7054567</v>
+        <v>7054965</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3264,7 +3247,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3274,7 +3257,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3326,7 +3309,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124233935</v>
+        <v>124235081</v>
       </c>
       <c r="B21" t="n">
         <v>91030</v>
@@ -3371,13 +3354,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466049</v>
+        <v>466058</v>
       </c>
       <c r="R21" t="n">
-        <v>7054622</v>
+        <v>7054681</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3404,24 +3387,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3473,10 +3446,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124236835</v>
+        <v>124233935</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3489,37 +3462,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466084</v>
+        <v>466049</v>
       </c>
       <c r="R22" t="n">
-        <v>7054927</v>
+        <v>7054622</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3548,7 +3526,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3558,7 +3536,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3587,12 +3570,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3610,10 +3593,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124238954</v>
+        <v>124234435</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3626,37 +3609,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466048</v>
+        <v>466046</v>
       </c>
       <c r="R23" t="n">
-        <v>7054406</v>
+        <v>7054578</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3685,7 +3673,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3695,7 +3683,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3724,12 +3712,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3747,7 +3735,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124235290</v>
+        <v>124238072</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3787,13 +3775,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466069</v>
+        <v>466028</v>
       </c>
       <c r="R24" t="n">
-        <v>7054731</v>
+        <v>7054700</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3822,7 +3810,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3832,7 +3820,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3861,12 +3849,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3884,10 +3872,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124233335</v>
+        <v>124233387</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3900,34 +3888,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466029</v>
+        <v>466025</v>
       </c>
       <c r="R25" t="n">
-        <v>7054621</v>
+        <v>7054632</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3959,7 +3952,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3969,7 +3962,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3998,12 +3991,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4021,10 +4014,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124230947</v>
+        <v>124238716</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4033,55 +4026,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466100</v>
+        <v>466019</v>
       </c>
       <c r="R26" t="n">
-        <v>7054439</v>
+        <v>7054567</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4110,7 +4089,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4120,7 +4099,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4135,6 +4114,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4152,7 +4151,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124234661</v>
+        <v>124236542</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -4188,17 +4187,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466088</v>
+        <v>466114</v>
       </c>
       <c r="R27" t="n">
-        <v>7054654</v>
+        <v>7054930</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4227,7 +4226,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4237,7 +4236,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4289,7 +4288,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124231227</v>
+        <v>124237519</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -4329,13 +4328,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466082</v>
+        <v>466024</v>
       </c>
       <c r="R28" t="n">
-        <v>7054428</v>
+        <v>7054752</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4364,7 +4363,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4374,7 +4373,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4391,16 +4390,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM28" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -4408,7 +4397,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4426,7 +4415,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124229492</v>
+        <v>124236233</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -4462,17 +4451,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466104</v>
+        <v>466113</v>
       </c>
       <c r="R29" t="n">
-        <v>7054370</v>
+        <v>7054849</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4501,7 +4490,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4511,7 +4500,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4525,7 +4514,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4563,10 +4552,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124236594</v>
+        <v>124233428</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4575,20 +4564,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4596,39 +4585,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466108</v>
+        <v>466026</v>
       </c>
       <c r="R30" t="n">
-        <v>7054934</v>
+        <v>7054647</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4657,7 +4632,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4667,7 +4642,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4682,6 +4662,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4699,14 +4699,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124232050</v>
+        <v>124231714</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4715,32 +4715,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4749,13 +4744,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466045</v>
+        <v>466077</v>
       </c>
       <c r="R31" t="n">
-        <v>7054447</v>
+        <v>7054405</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4784,7 +4779,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4794,12 +4789,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4851,14 +4841,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124231714</v>
+        <v>124232609</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4867,27 +4857,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4896,13 +4893,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466077</v>
+        <v>466085</v>
       </c>
       <c r="R32" t="n">
-        <v>7054405</v>
+        <v>7054527</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4931,7 +4928,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4941,7 +4938,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4993,7 +4995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124228589</v>
+        <v>124237622</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5034,14 +5036,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466066</v>
+        <v>466053</v>
       </c>
       <c r="R33" t="n">
-        <v>7054389</v>
+        <v>7054770</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -5073,7 +5075,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5083,7 +5085,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5287,7 +5289,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124228388</v>
+        <v>124235016</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5332,13 +5334,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466017</v>
+        <v>466066</v>
       </c>
       <c r="R35" t="n">
-        <v>7054386</v>
+        <v>7054677</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5367,7 +5369,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5377,12 +5379,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5411,12 +5413,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5581,7 +5583,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124229096</v>
+        <v>124237940</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5615,27 +5617,29 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466061</v>
+        <v>466040</v>
       </c>
       <c r="R37" t="n">
-        <v>7054411</v>
+        <v>7054768</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5664,7 +5668,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5674,12 +5678,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5731,7 +5735,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124230274</v>
+        <v>124232959</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5767,7 +5771,12 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5776,13 +5785,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466120</v>
+        <v>466071</v>
       </c>
       <c r="R38" t="n">
-        <v>7054456</v>
+        <v>7054484</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5811,7 +5820,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5821,12 +5830,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5878,7 +5887,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124232959</v>
+        <v>124229096</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5912,26 +5921,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466071</v>
+        <v>466061</v>
       </c>
       <c r="R39" t="n">
-        <v>7054484</v>
+        <v>7054411</v>
       </c>
       <c r="S39" t="n">
         <v>12</v>
@@ -5963,7 +5970,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5973,12 +5980,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6030,14 +6037,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124233428</v>
+        <v>124232050</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6046,16 +6053,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6069,19 +6076,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466026</v>
+        <v>466045</v>
       </c>
       <c r="R40" t="n">
-        <v>7054647</v>
+        <v>7054447</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6110,7 +6122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6120,12 +6132,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6177,7 +6189,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124235393</v>
+        <v>124228589</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6222,13 +6234,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466051</v>
+        <v>466066</v>
       </c>
       <c r="R41" t="n">
-        <v>7054737</v>
+        <v>7054389</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6257,7 +6269,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6267,7 +6279,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6324,7 +6336,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124237940</v>
+        <v>124236498</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6360,27 +6372,22 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466040</v>
+        <v>466123</v>
       </c>
       <c r="R42" t="n">
-        <v>7054768</v>
+        <v>7054939</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6409,7 +6416,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6419,12 +6426,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6476,7 +6483,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124236498</v>
+        <v>124230274</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6512,22 +6519,22 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466123</v>
+        <v>466120</v>
       </c>
       <c r="R43" t="n">
-        <v>7054939</v>
+        <v>7054456</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6556,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6566,12 +6573,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6770,7 +6777,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124232609</v>
+        <v>124228388</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6804,16 +6811,9 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6822,13 +6822,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466085</v>
+        <v>466017</v>
       </c>
       <c r="R45" t="n">
-        <v>7054527</v>
+        <v>7054386</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124237622</v>
+        <v>124235393</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6965,17 +6965,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466053</v>
+        <v>466051</v>
       </c>
       <c r="R46" t="n">
-        <v>7054770</v>
+        <v>7054737</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124229168</v>
+        <v>124235851</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,60 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466061</v>
+        <v>466040</v>
       </c>
       <c r="R2" t="n">
-        <v>7054409</v>
+        <v>7054923</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,6 +775,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124235507</v>
+        <v>124235081</v>
       </c>
       <c r="B3" t="n">
         <v>91030</v>
@@ -856,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466047</v>
+        <v>466058</v>
       </c>
       <c r="R3" t="n">
-        <v>7054739</v>
+        <v>7054681</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,19 +890,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:42</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124233335</v>
+        <v>124231450</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,37 +965,56 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466029</v>
+        <v>466113</v>
       </c>
       <c r="R4" t="n">
-        <v>7054621</v>
+        <v>7054408</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1038,7 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,26 +1073,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124237831</v>
+        <v>124233387</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1131,14 +1131,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466048</v>
+        <v>466025</v>
       </c>
       <c r="R5" t="n">
-        <v>7054795</v>
+        <v>7054632</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124236594</v>
+        <v>124230947</v>
       </c>
       <c r="B6" t="n">
         <v>57883</v>
@@ -1280,24 +1280,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466108</v>
+        <v>466100</v>
       </c>
       <c r="R6" t="n">
-        <v>7054934</v>
+        <v>7054439</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1326,7 +1321,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1336,7 +1331,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1368,10 +1363,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124236835</v>
+        <v>124237831</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,37 +1379,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466084</v>
+        <v>466048</v>
       </c>
       <c r="R7" t="n">
-        <v>7054927</v>
+        <v>7054795</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124235290</v>
+        <v>124238954</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466069</v>
+        <v>466048</v>
       </c>
       <c r="R8" t="n">
-        <v>7054731</v>
+        <v>7054406</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124229492</v>
+        <v>124234661</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466104</v>
+        <v>466088</v>
       </c>
       <c r="R9" t="n">
-        <v>7054370</v>
+        <v>7054654</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124234661</v>
+        <v>124238409</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1795,37 +1795,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466088</v>
+        <v>466019</v>
       </c>
       <c r="R10" t="n">
-        <v>7054654</v>
+        <v>7054696</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1854,7 +1859,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1864,7 +1869,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1893,12 +1903,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1916,10 +1926,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124238409</v>
+        <v>124233935</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1932,27 +1942,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1961,13 +1971,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466019</v>
+        <v>466049</v>
       </c>
       <c r="R11" t="n">
-        <v>7054696</v>
+        <v>7054622</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,7 +2006,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2006,12 +2016,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2040,12 +2050,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2063,10 +2073,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124234049</v>
+        <v>124237519</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2079,42 +2089,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466057</v>
+        <v>466024</v>
       </c>
       <c r="R12" t="n">
-        <v>7054600</v>
+        <v>7054752</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2143,7 +2148,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2153,7 +2158,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2170,24 +2175,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2205,10 +2200,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230947</v>
+        <v>124236542</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2217,55 +2212,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466100</v>
+        <v>466114</v>
       </c>
       <c r="R13" t="n">
-        <v>7054439</v>
+        <v>7054930</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2294,7 +2275,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2304,7 +2285,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2319,6 +2300,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2336,7 +2337,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124235851</v>
+        <v>124238716</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2372,17 +2373,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466040</v>
+        <v>466019</v>
       </c>
       <c r="R14" t="n">
-        <v>7054923</v>
+        <v>7054567</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2411,7 +2412,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2421,7 +2422,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2473,10 +2474,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124231450</v>
+        <v>124236594</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2485,25 +2486,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2528,17 +2529,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466113</v>
+        <v>466108</v>
       </c>
       <c r="R15" t="n">
-        <v>7054408</v>
+        <v>7054934</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2567,7 +2568,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2577,12 +2578,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2751,7 +2747,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124238954</v>
+        <v>124236910</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2787,17 +2783,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466048</v>
+        <v>466024</v>
       </c>
       <c r="R17" t="n">
-        <v>7054406</v>
+        <v>7054965</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2826,7 +2822,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2836,7 +2832,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2888,7 +2884,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124232343</v>
+        <v>124234435</v>
       </c>
       <c r="B18" t="n">
         <v>91030</v>
@@ -2933,13 +2929,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466050</v>
+        <v>466046</v>
       </c>
       <c r="R18" t="n">
-        <v>7054470</v>
+        <v>7054578</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2968,7 +2964,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2978,12 +2974,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3012,12 +3003,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3035,7 +3026,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124231227</v>
+        <v>124236835</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -3071,17 +3062,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466082</v>
+        <v>466084</v>
       </c>
       <c r="R19" t="n">
-        <v>7054428</v>
+        <v>7054927</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3110,7 +3101,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3120,7 +3111,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3172,7 +3163,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124236910</v>
+        <v>124233335</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -3208,17 +3199,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466024</v>
+        <v>466029</v>
       </c>
       <c r="R20" t="n">
-        <v>7054965</v>
+        <v>7054621</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3247,7 +3238,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3257,7 +3248,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3309,10 +3300,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124235081</v>
+        <v>124238072</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3325,42 +3316,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466058</v>
+        <v>466028</v>
       </c>
       <c r="R21" t="n">
-        <v>7054681</v>
+        <v>7054700</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3387,14 +3373,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3423,12 +3414,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3446,10 +3437,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124233935</v>
+        <v>124231227</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3462,39 +3453,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466049</v>
+        <v>466082</v>
       </c>
       <c r="R22" t="n">
-        <v>7054622</v>
+        <v>7054428</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3526,7 +3512,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3536,12 +3522,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3570,12 +3551,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3593,10 +3574,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124234435</v>
+        <v>124229168</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3605,31 +3586,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3638,13 +3633,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466046</v>
+        <v>466061</v>
       </c>
       <c r="R23" t="n">
-        <v>7054578</v>
+        <v>7054409</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3673,7 +3668,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3683,7 +3678,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3698,26 +3693,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3735,7 +3710,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124238072</v>
+        <v>124229492</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3775,13 +3750,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466028</v>
+        <v>466104</v>
       </c>
       <c r="R24" t="n">
-        <v>7054700</v>
+        <v>7054370</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3810,7 +3785,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3820,7 +3795,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3872,7 +3847,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124233387</v>
+        <v>124235507</v>
       </c>
       <c r="B25" t="n">
         <v>91030</v>
@@ -3917,13 +3892,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466025</v>
+        <v>466047</v>
       </c>
       <c r="R25" t="n">
-        <v>7054632</v>
+        <v>7054739</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3952,7 +3927,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3962,7 +3937,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3991,12 +3966,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4014,7 +3989,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124238716</v>
+        <v>124235290</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -4054,10 +4029,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466019</v>
+        <v>466069</v>
       </c>
       <c r="R26" t="n">
-        <v>7054567</v>
+        <v>7054731</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -4089,7 +4064,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4099,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4128,12 +4103,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4151,10 +4126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124236542</v>
+        <v>124234049</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4167,37 +4142,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466114</v>
+        <v>466057</v>
       </c>
       <c r="R27" t="n">
-        <v>7054930</v>
+        <v>7054600</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4226,7 +4206,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4236,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4265,12 +4245,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4288,7 +4268,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124237519</v>
+        <v>124236233</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -4324,17 +4304,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466024</v>
+        <v>466113</v>
       </c>
       <c r="R28" t="n">
-        <v>7054752</v>
+        <v>7054849</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4363,7 +4343,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4373,7 +4353,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4387,7 +4367,17 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -4397,7 +4387,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4415,10 +4405,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124236233</v>
+        <v>124232343</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4431,37 +4421,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466113</v>
+        <v>466050</v>
       </c>
       <c r="R29" t="n">
-        <v>7054849</v>
+        <v>7054470</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4500,7 +4495,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124233428</v>
+        <v>124231714</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4568,27 +4568,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466026</v>
+        <v>466077</v>
       </c>
       <c r="R30" t="n">
-        <v>7054647</v>
+        <v>7054405</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4642,12 +4642,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4699,10 +4694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124231714</v>
+        <v>124233428</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4715,27 +4710,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4744,13 +4739,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466077</v>
+        <v>466026</v>
       </c>
       <c r="R31" t="n">
-        <v>7054405</v>
+        <v>7054647</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4779,7 +4774,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4789,7 +4784,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124232609</v>
+        <v>124237940</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4875,8 +4875,6 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4889,14 +4887,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466085</v>
+        <v>466040</v>
       </c>
       <c r="R32" t="n">
-        <v>7054527</v>
+        <v>7054768</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4928,7 +4926,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4938,12 +4936,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4995,7 +4993,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124237622</v>
+        <v>124232959</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5034,19 +5032,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466053</v>
+        <v>466071</v>
       </c>
       <c r="R33" t="n">
-        <v>7054770</v>
+        <v>7054484</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5075,7 +5078,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5085,12 +5088,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5142,7 +5145,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124228749</v>
+        <v>124235393</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5178,7 +5181,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5187,13 +5190,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466066</v>
+        <v>466051</v>
       </c>
       <c r="R34" t="n">
-        <v>7054397</v>
+        <v>7054737</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5222,7 +5225,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5232,12 +5235,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5289,7 +5292,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124235016</v>
+        <v>124232050</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5325,7 +5328,12 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5334,13 +5342,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466066</v>
+        <v>466045</v>
       </c>
       <c r="R35" t="n">
-        <v>7054677</v>
+        <v>7054447</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5369,7 +5377,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5379,12 +5387,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5413,12 +5421,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5436,7 +5444,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124233675</v>
+        <v>124230274</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5481,13 +5489,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466039</v>
+        <v>466120</v>
       </c>
       <c r="R36" t="n">
-        <v>7054631</v>
+        <v>7054456</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5526,12 +5534,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5583,7 +5591,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124237940</v>
+        <v>124229096</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5617,29 +5625,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466040</v>
+        <v>466061</v>
       </c>
       <c r="R37" t="n">
-        <v>7054768</v>
+        <v>7054411</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5668,7 +5674,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5678,12 +5684,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5735,7 +5741,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124232959</v>
+        <v>124235016</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5774,21 +5780,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466071</v>
+        <v>466066</v>
       </c>
       <c r="R38" t="n">
-        <v>7054484</v>
+        <v>7054677</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
@@ -5820,7 +5821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5830,12 +5831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5864,12 +5865,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5887,7 +5888,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124229096</v>
+        <v>124228388</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5921,27 +5922,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466061</v>
+        <v>466017</v>
       </c>
       <c r="R39" t="n">
-        <v>7054411</v>
+        <v>7054386</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5970,7 +5968,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5980,12 +5978,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6037,7 +6035,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124232050</v>
+        <v>124228749</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6076,24 +6074,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466045</v>
+        <v>466066</v>
       </c>
       <c r="R40" t="n">
-        <v>7054447</v>
+        <v>7054397</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6122,7 +6115,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6132,12 +6125,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6189,7 +6182,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124228589</v>
+        <v>124236498</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6230,17 +6223,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466066</v>
+        <v>466123</v>
       </c>
       <c r="R41" t="n">
-        <v>7054389</v>
+        <v>7054939</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6269,7 +6262,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6279,12 +6272,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6336,7 +6329,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124236498</v>
+        <v>124232609</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6370,24 +6363,31 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466123</v>
+        <v>466085</v>
       </c>
       <c r="R42" t="n">
-        <v>7054939</v>
+        <v>7054527</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6483,7 +6483,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124230274</v>
+        <v>124231120</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6519,7 +6519,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6528,13 +6528,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466120</v>
+        <v>466086</v>
       </c>
       <c r="R43" t="n">
-        <v>7054456</v>
+        <v>7054427</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6630,7 +6630,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124231120</v>
+        <v>124233675</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6666,7 +6666,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6675,13 +6675,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466086</v>
+        <v>466039</v>
       </c>
       <c r="R44" t="n">
-        <v>7054427</v>
+        <v>7054631</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124228388</v>
+        <v>124237622</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6818,17 +6818,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466017</v>
+        <v>466053</v>
       </c>
       <c r="R45" t="n">
-        <v>7054386</v>
+        <v>7054770</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124235393</v>
+        <v>124228589</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466051</v>
+        <v>466066</v>
       </c>
       <c r="R46" t="n">
-        <v>7054737</v>
+        <v>7054389</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -2474,10 +2474,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124236594</v>
+        <v>124233251</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2486,60 +2486,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466108</v>
+        <v>466029</v>
       </c>
       <c r="R15" t="n">
-        <v>7054934</v>
+        <v>7054550</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2568,7 +2549,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2578,7 +2559,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2593,6 +2574,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2610,10 +2611,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124233251</v>
+        <v>124236594</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2622,41 +2623,60 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466029</v>
+        <v>466108</v>
       </c>
       <c r="R16" t="n">
-        <v>7054550</v>
+        <v>7054934</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2685,7 +2705,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2695,7 +2715,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2710,26 +2730,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124235507</v>
+        <v>124235290</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3863,39 +3863,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466047</v>
+        <v>466069</v>
       </c>
       <c r="R25" t="n">
-        <v>7054739</v>
+        <v>7054731</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
@@ -3927,7 +3922,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3937,7 +3932,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3966,12 +3961,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3989,10 +3984,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124235290</v>
+        <v>124235507</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4005,34 +4000,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466069</v>
+        <v>466047</v>
       </c>
       <c r="R26" t="n">
-        <v>7054731</v>
+        <v>7054739</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124235851</v>
+        <v>124238072</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466040</v>
+        <v>466028</v>
       </c>
       <c r="R2" t="n">
-        <v>7054923</v>
+        <v>7054700</v>
       </c>
       <c r="S2" t="n">
         <v>11</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124235081</v>
+        <v>124238954</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466058</v>
+        <v>466048</v>
       </c>
       <c r="R3" t="n">
-        <v>7054681</v>
+        <v>7054406</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,14 +885,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124231450</v>
+        <v>124236233</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,56 +965,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>466113</v>
       </c>
       <c r="R4" t="n">
-        <v>7054408</v>
+        <v>7054849</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,7 +1048,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,7 +1086,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124233387</v>
+        <v>124237831</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1131,14 +1127,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466025</v>
+        <v>466048</v>
       </c>
       <c r="R5" t="n">
-        <v>7054632</v>
+        <v>7054795</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1170,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,7 +1176,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,12 +1205,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,10 +1228,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124230947</v>
+        <v>124233935</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1244,40 +1240,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1286,13 +1273,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466100</v>
+        <v>466049</v>
       </c>
       <c r="R6" t="n">
-        <v>7054439</v>
+        <v>7054622</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1321,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1331,7 +1318,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,6 +1338,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1363,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124237831</v>
+        <v>124237519</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1379,42 +1391,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466048</v>
+        <v>466024</v>
       </c>
       <c r="R7" t="n">
-        <v>7054795</v>
+        <v>7054752</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1443,7 +1450,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,7 +1460,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1470,24 +1477,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1505,10 +1502,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124238954</v>
+        <v>124235081</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1521,37 +1518,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466048</v>
+        <v>466058</v>
       </c>
       <c r="R8" t="n">
-        <v>7054406</v>
+        <v>7054681</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1578,19 +1580,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:19</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1619,12 +1616,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1642,10 +1639,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124234661</v>
+        <v>124236594</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1654,41 +1651,60 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466088</v>
+        <v>466108</v>
       </c>
       <c r="R9" t="n">
-        <v>7054654</v>
+        <v>7054934</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1717,7 +1733,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1727,7 +1743,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1742,26 +1758,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1779,10 +1775,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124238409</v>
+        <v>124238716</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1795,29 +1791,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
@@ -1827,7 +1818,7 @@
         <v>466019</v>
       </c>
       <c r="R10" t="n">
-        <v>7054696</v>
+        <v>7054567</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1859,7 +1850,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1869,12 +1860,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1903,12 +1889,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1926,10 +1912,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124233935</v>
+        <v>124229168</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1938,31 +1924,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466049</v>
+        <v>466061</v>
       </c>
       <c r="R11" t="n">
-        <v>7054622</v>
+        <v>7054409</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2016,12 +2016,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2036,26 +2031,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2073,7 +2048,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124237519</v>
+        <v>124235851</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -2109,17 +2084,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466024</v>
+        <v>466040</v>
       </c>
       <c r="R12" t="n">
-        <v>7054752</v>
+        <v>7054923</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2148,7 +2123,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2158,7 +2133,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2175,6 +2150,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM12" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2182,7 +2167,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2200,10 +2185,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124236542</v>
+        <v>124234049</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,37 +2201,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466114</v>
+        <v>466057</v>
       </c>
       <c r="R13" t="n">
-        <v>7054930</v>
+        <v>7054600</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2275,7 +2265,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2285,7 +2275,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2314,12 +2304,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2337,7 +2327,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124238716</v>
+        <v>124231227</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2377,13 +2367,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466019</v>
+        <v>466082</v>
       </c>
       <c r="R14" t="n">
-        <v>7054567</v>
+        <v>7054428</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2412,7 +2402,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2422,7 +2412,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2474,7 +2464,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124233251</v>
+        <v>124236910</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2510,17 +2500,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466029</v>
+        <v>466024</v>
       </c>
       <c r="R15" t="n">
-        <v>7054550</v>
+        <v>7054965</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2549,7 +2539,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2559,7 +2549,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2611,10 +2601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124236594</v>
+        <v>124236542</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2623,60 +2613,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466108</v>
+        <v>466114</v>
       </c>
       <c r="R16" t="n">
-        <v>7054934</v>
+        <v>7054930</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2705,7 +2676,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2715,7 +2686,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2730,6 +2701,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2747,7 +2738,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124236910</v>
+        <v>124233251</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2783,17 +2774,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466024</v>
+        <v>466029</v>
       </c>
       <c r="R17" t="n">
-        <v>7054965</v>
+        <v>7054550</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2822,7 +2813,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2832,7 +2823,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2884,10 +2875,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124234435</v>
+        <v>124233335</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2900,42 +2891,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466046</v>
+        <v>466029</v>
       </c>
       <c r="R18" t="n">
-        <v>7054578</v>
+        <v>7054621</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2964,7 +2950,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2974,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3003,12 +2989,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3026,10 +3012,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124236835</v>
+        <v>124235507</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3042,37 +3028,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466084</v>
+        <v>466047</v>
       </c>
       <c r="R19" t="n">
-        <v>7054927</v>
+        <v>7054739</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3101,7 +3092,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3111,7 +3102,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3140,12 +3131,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3163,10 +3154,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124233335</v>
+        <v>124238409</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3179,37 +3170,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466029</v>
+        <v>466019</v>
       </c>
       <c r="R20" t="n">
-        <v>7054621</v>
+        <v>7054696</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3238,7 +3234,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3248,7 +3244,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3277,12 +3278,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3300,7 +3301,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124238072</v>
+        <v>124234661</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -3340,13 +3341,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466028</v>
+        <v>466088</v>
       </c>
       <c r="R21" t="n">
-        <v>7054700</v>
+        <v>7054654</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3375,7 +3376,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3385,7 +3386,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3437,7 +3438,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124231227</v>
+        <v>124229492</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3477,13 +3478,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466082</v>
+        <v>466104</v>
       </c>
       <c r="R22" t="n">
-        <v>7054428</v>
+        <v>7054370</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3512,7 +3513,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3522,7 +3523,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3574,10 +3575,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124229168</v>
+        <v>124233387</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3586,45 +3587,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3633,13 +3620,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466061</v>
+        <v>466025</v>
       </c>
       <c r="R23" t="n">
-        <v>7054409</v>
+        <v>7054632</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3668,7 +3655,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3678,7 +3665,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3693,6 +3680,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3710,10 +3717,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124229492</v>
+        <v>124230947</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3722,41 +3729,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466104</v>
+        <v>466100</v>
       </c>
       <c r="R24" t="n">
-        <v>7054370</v>
+        <v>7054439</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3785,7 +3806,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3795,7 +3816,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3810,26 +3831,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3847,7 +3848,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124235290</v>
+        <v>124236835</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3883,17 +3884,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466069</v>
+        <v>466084</v>
       </c>
       <c r="R25" t="n">
-        <v>7054731</v>
+        <v>7054927</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3922,7 +3923,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3932,7 +3933,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3961,12 +3962,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3984,10 +3985,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124235507</v>
+        <v>124231450</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4000,27 +4001,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4029,13 +4044,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466047</v>
+        <v>466113</v>
       </c>
       <c r="R26" t="n">
-        <v>7054739</v>
+        <v>7054408</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4064,7 +4079,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4074,7 +4089,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4089,26 +4109,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124234049</v>
+        <v>124232343</v>
       </c>
       <c r="B27" t="n">
         <v>91030</v>
@@ -4171,13 +4171,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466057</v>
+        <v>466050</v>
       </c>
       <c r="R27" t="n">
-        <v>7054600</v>
+        <v>7054470</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4216,7 +4216,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4268,10 +4273,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124236233</v>
+        <v>124234435</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4284,37 +4289,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466113</v>
+        <v>466046</v>
       </c>
       <c r="R28" t="n">
-        <v>7054849</v>
+        <v>7054578</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4343,7 +4353,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4353,7 +4363,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4367,7 +4377,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4382,12 +4392,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4405,10 +4415,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124232343</v>
+        <v>124235290</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4421,42 +4431,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466050</v>
+        <v>466069</v>
       </c>
       <c r="R29" t="n">
-        <v>7054470</v>
+        <v>7054731</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4485,7 +4490,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4495,12 +4500,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124232959</v>
+        <v>124236498</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5032,21 +5032,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466071</v>
+        <v>466123</v>
       </c>
       <c r="R33" t="n">
-        <v>7054484</v>
+        <v>7054939</v>
       </c>
       <c r="S33" t="n">
         <v>12</v>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5088,12 +5083,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5292,7 +5287,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124232050</v>
+        <v>124232609</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5326,6 +5321,8 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -5342,13 +5339,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466045</v>
+        <v>466085</v>
       </c>
       <c r="R35" t="n">
-        <v>7054447</v>
+        <v>7054527</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5377,7 +5374,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5387,12 +5384,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5444,7 +5441,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124230274</v>
+        <v>124231120</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5480,7 +5477,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5489,13 +5486,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466120</v>
+        <v>466086</v>
       </c>
       <c r="R36" t="n">
-        <v>7054456</v>
+        <v>7054427</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5524,7 +5521,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5534,12 +5531,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5591,7 +5588,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124229096</v>
+        <v>124237622</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5625,27 +5622,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466061</v>
+        <v>466053</v>
       </c>
       <c r="R37" t="n">
-        <v>7054411</v>
+        <v>7054770</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5674,7 +5668,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5684,12 +5678,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5741,7 +5735,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124235016</v>
+        <v>124229096</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5775,21 +5769,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466066</v>
+        <v>466061</v>
       </c>
       <c r="R38" t="n">
-        <v>7054677</v>
+        <v>7054411</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
@@ -5821,7 +5818,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5831,12 +5828,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5865,12 +5862,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5888,7 +5885,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124228388</v>
+        <v>124232959</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5927,19 +5924,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466017</v>
+        <v>466071</v>
       </c>
       <c r="R39" t="n">
-        <v>7054386</v>
+        <v>7054484</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5968,7 +5970,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5978,12 +5980,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6035,7 +6037,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124228749</v>
+        <v>124230274</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6080,13 +6082,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466066</v>
+        <v>466120</v>
       </c>
       <c r="R40" t="n">
-        <v>7054397</v>
+        <v>7054456</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6115,7 +6117,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6125,12 +6127,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6182,7 +6184,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124236498</v>
+        <v>124228589</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6223,17 +6225,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466123</v>
+        <v>466066</v>
       </c>
       <c r="R41" t="n">
-        <v>7054939</v>
+        <v>7054389</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6262,7 +6264,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6272,12 +6274,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6329,7 +6331,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124232609</v>
+        <v>124233675</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6363,28 +6365,21 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466085</v>
+        <v>466039</v>
       </c>
       <c r="R42" t="n">
-        <v>7054527</v>
+        <v>7054631</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6426,12 +6421,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6483,7 +6478,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124231120</v>
+        <v>124232050</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6519,7 +6514,12 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6528,13 +6528,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466086</v>
+        <v>466045</v>
       </c>
       <c r="R43" t="n">
-        <v>7054427</v>
+        <v>7054447</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6630,7 +6630,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124233675</v>
+        <v>124228749</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6675,13 +6675,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466039</v>
+        <v>466066</v>
       </c>
       <c r="R44" t="n">
-        <v>7054631</v>
+        <v>7054397</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124237622</v>
+        <v>124235016</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6818,17 +6818,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466053</v>
+        <v>466066</v>
       </c>
       <c r="R45" t="n">
-        <v>7054770</v>
+        <v>7054677</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124228589</v>
+        <v>124228388</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466066</v>
+        <v>466017</v>
       </c>
       <c r="R46" t="n">
-        <v>7054389</v>
+        <v>7054386</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -1375,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124237519</v>
+        <v>124236594</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1387,41 +1387,60 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466024</v>
+        <v>466108</v>
       </c>
       <c r="R7" t="n">
-        <v>7054752</v>
+        <v>7054934</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1450,7 +1469,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1460,7 +1479,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,16 +1494,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1502,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124235081</v>
+        <v>124237519</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1518,42 +1527,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466058</v>
+        <v>466024</v>
       </c>
       <c r="R8" t="n">
-        <v>7054681</v>
+        <v>7054752</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1580,14 +1584,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,24 +1613,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1639,10 +1638,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124236594</v>
+        <v>124235081</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1651,60 +1650,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466108</v>
+        <v>466058</v>
       </c>
       <c r="R9" t="n">
-        <v>7054934</v>
+        <v>7054681</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1731,19 +1716,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:12</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,6 +1738,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124238072</v>
+        <v>124234049</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466028</v>
+        <v>466057</v>
       </c>
       <c r="R2" t="n">
-        <v>7054700</v>
+        <v>7054600</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124238954</v>
+        <v>124230947</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,41 +829,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466048</v>
+        <v>466100</v>
       </c>
       <c r="R3" t="n">
-        <v>7054406</v>
+        <v>7054439</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +906,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +916,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,26 +931,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,7 +948,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124236233</v>
+        <v>124233251</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -985,14 +984,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466113</v>
+        <v>466029</v>
       </c>
       <c r="R4" t="n">
-        <v>7054849</v>
+        <v>7054550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1023,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1033,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,7 +1047,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1086,10 +1085,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124237831</v>
+        <v>124231227</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,39 +1101,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466048</v>
+        <v>466082</v>
       </c>
       <c r="R5" t="n">
-        <v>7054795</v>
+        <v>7054428</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1166,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1176,7 +1170,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,12 +1199,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1375,7 +1369,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124236594</v>
+        <v>124229168</v>
       </c>
       <c r="B7" t="n">
         <v>57883</v>
@@ -1430,17 +1424,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466108</v>
+        <v>466061</v>
       </c>
       <c r="R7" t="n">
-        <v>7054934</v>
+        <v>7054409</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1469,7 +1463,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1479,7 +1473,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1511,7 +1505,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124237519</v>
+        <v>124238716</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1551,13 +1545,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466024</v>
+        <v>466019</v>
       </c>
       <c r="R8" t="n">
-        <v>7054752</v>
+        <v>7054567</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1586,7 +1580,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1596,7 +1590,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1613,6 +1607,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1620,7 +1624,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1638,10 +1642,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124235081</v>
+        <v>124236542</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1654,42 +1658,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466058</v>
+        <v>466114</v>
       </c>
       <c r="R9" t="n">
-        <v>7054681</v>
+        <v>7054930</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1716,14 +1715,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1752,12 +1756,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1775,7 +1779,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124238716</v>
+        <v>124236835</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1811,17 +1815,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466019</v>
+        <v>466084</v>
       </c>
       <c r="R10" t="n">
-        <v>7054567</v>
+        <v>7054927</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1850,7 +1854,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1860,7 +1864,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1912,10 +1916,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124229168</v>
+        <v>124235081</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1924,45 +1928,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1971,13 +1961,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466061</v>
+        <v>466058</v>
       </c>
       <c r="R11" t="n">
-        <v>7054409</v>
+        <v>7054681</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2004,19 +1994,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:02</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,6 +2016,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2048,7 +2053,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124235851</v>
+        <v>124236233</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -2084,17 +2089,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466040</v>
+        <v>466113</v>
       </c>
       <c r="R12" t="n">
-        <v>7054923</v>
+        <v>7054849</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2123,7 +2128,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2133,7 +2138,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2147,7 +2152,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2185,10 +2190,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124234049</v>
+        <v>124233335</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,42 +2206,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466057</v>
+        <v>466029</v>
       </c>
       <c r="R13" t="n">
-        <v>7054600</v>
+        <v>7054621</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124231227</v>
+        <v>124235507</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2343,37 +2343,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466082</v>
+        <v>466047</v>
       </c>
       <c r="R14" t="n">
-        <v>7054428</v>
+        <v>7054739</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2402,7 +2407,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2412,7 +2417,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2441,12 +2446,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2464,7 +2469,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124236910</v>
+        <v>124238072</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2500,17 +2505,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466024</v>
+        <v>466028</v>
       </c>
       <c r="R15" t="n">
-        <v>7054965</v>
+        <v>7054700</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2539,7 +2544,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2549,7 +2554,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2601,7 +2606,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124236542</v>
+        <v>124235851</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2637,17 +2642,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466114</v>
+        <v>466040</v>
       </c>
       <c r="R16" t="n">
-        <v>7054930</v>
+        <v>7054923</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2676,7 +2681,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2686,7 +2691,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2738,10 +2743,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124233251</v>
+        <v>124236594</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2750,41 +2755,60 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466029</v>
+        <v>466108</v>
       </c>
       <c r="R17" t="n">
-        <v>7054550</v>
+        <v>7054934</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2813,7 +2837,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2823,7 +2847,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2838,26 +2862,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2875,10 +2879,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124233335</v>
+        <v>124233387</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2891,34 +2895,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466029</v>
+        <v>466025</v>
       </c>
       <c r="R18" t="n">
-        <v>7054621</v>
+        <v>7054632</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2950,7 +2959,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2960,7 +2969,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2989,12 +2998,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3012,7 +3021,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124235507</v>
+        <v>124234435</v>
       </c>
       <c r="B19" t="n">
         <v>91030</v>
@@ -3057,13 +3066,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466047</v>
+        <v>466046</v>
       </c>
       <c r="R19" t="n">
-        <v>7054739</v>
+        <v>7054578</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3092,7 +3101,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3102,7 +3111,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3301,7 +3310,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124234661</v>
+        <v>124237519</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -3341,13 +3350,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466088</v>
+        <v>466024</v>
       </c>
       <c r="R21" t="n">
-        <v>7054654</v>
+        <v>7054752</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3376,7 +3385,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3386,7 +3395,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3403,16 +3412,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM21" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3420,7 +3419,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3438,7 +3437,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124229492</v>
+        <v>124236910</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3474,17 +3473,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466104</v>
+        <v>466024</v>
       </c>
       <c r="R22" t="n">
-        <v>7054370</v>
+        <v>7054965</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3513,7 +3512,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3523,7 +3522,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3575,10 +3574,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124233387</v>
+        <v>124238954</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3591,39 +3590,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466025</v>
+        <v>466048</v>
       </c>
       <c r="R23" t="n">
-        <v>7054632</v>
+        <v>7054406</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3655,7 +3649,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3665,7 +3659,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3694,12 +3688,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3717,10 +3711,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124230947</v>
+        <v>124229492</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3729,55 +3723,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466100</v>
+        <v>466104</v>
       </c>
       <c r="R24" t="n">
-        <v>7054439</v>
+        <v>7054370</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3806,7 +3786,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3816,7 +3796,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3831,6 +3811,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124236835</v>
+        <v>124234661</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3884,17 +3884,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466084</v>
+        <v>466088</v>
       </c>
       <c r="R25" t="n">
-        <v>7054927</v>
+        <v>7054654</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3985,10 +3985,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124231450</v>
+        <v>124235290</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4001,56 +4001,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466113</v>
+        <v>466069</v>
       </c>
       <c r="R26" t="n">
-        <v>7054408</v>
+        <v>7054731</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4079,7 +4060,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4089,12 +4070,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4109,6 +4085,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4126,10 +4122,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124232343</v>
+        <v>124231450</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4142,27 +4138,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4171,13 +4181,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466050</v>
+        <v>466113</v>
       </c>
       <c r="R27" t="n">
-        <v>7054470</v>
+        <v>7054408</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4206,7 +4216,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4216,12 +4226,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4236,26 +4246,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4273,7 +4263,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124234435</v>
+        <v>124232343</v>
       </c>
       <c r="B28" t="n">
         <v>91030</v>
@@ -4318,13 +4308,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466046</v>
+        <v>466050</v>
       </c>
       <c r="R28" t="n">
-        <v>7054578</v>
+        <v>7054470</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4353,7 +4343,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4363,7 +4353,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4392,12 +4387,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4415,10 +4410,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124235290</v>
+        <v>124237831</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4431,37 +4426,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466069</v>
+        <v>466048</v>
       </c>
       <c r="R29" t="n">
-        <v>7054731</v>
+        <v>7054795</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124237940</v>
+        <v>124235393</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4877,27 +4877,22 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466040</v>
+        <v>466051</v>
       </c>
       <c r="R32" t="n">
-        <v>7054768</v>
+        <v>7054737</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4926,7 +4921,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4936,12 +4931,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4993,7 +4988,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124236498</v>
+        <v>124230274</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5029,22 +5024,22 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466123</v>
+        <v>466120</v>
       </c>
       <c r="R33" t="n">
-        <v>7054939</v>
+        <v>7054456</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5073,7 +5068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5083,12 +5078,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5140,7 +5135,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124235393</v>
+        <v>124228388</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5185,13 +5180,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466051</v>
+        <v>466017</v>
       </c>
       <c r="R34" t="n">
-        <v>7054737</v>
+        <v>7054386</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5220,7 +5215,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5230,12 +5225,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5287,7 +5282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124232609</v>
+        <v>124237622</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5321,28 +5316,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466085</v>
+        <v>466053</v>
       </c>
       <c r="R35" t="n">
-        <v>7054527</v>
+        <v>7054770</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -5374,7 +5362,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5384,12 +5372,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5441,7 +5429,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124231120</v>
+        <v>124232050</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5477,7 +5465,12 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5486,13 +5479,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466086</v>
+        <v>466045</v>
       </c>
       <c r="R36" t="n">
-        <v>7054427</v>
+        <v>7054447</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5521,7 +5514,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5531,12 +5524,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5588,7 +5581,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124237622</v>
+        <v>124229096</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5622,24 +5615,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466053</v>
+        <v>466061</v>
       </c>
       <c r="R37" t="n">
-        <v>7054770</v>
+        <v>7054411</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5668,7 +5664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5678,12 +5674,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5735,7 +5731,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124229096</v>
+        <v>124232609</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5773,23 +5769,27 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466061</v>
+        <v>466085</v>
       </c>
       <c r="R38" t="n">
-        <v>7054411</v>
+        <v>7054527</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6037,7 +6037,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124230274</v>
+        <v>124236498</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6073,22 +6073,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466120</v>
+        <v>466123</v>
       </c>
       <c r="R40" t="n">
-        <v>7054456</v>
+        <v>7054939</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6184,7 +6184,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124228589</v>
+        <v>124231120</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6229,13 +6229,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466066</v>
+        <v>466086</v>
       </c>
       <c r="R41" t="n">
-        <v>7054389</v>
+        <v>7054427</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6331,7 +6331,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124233675</v>
+        <v>124228749</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6376,13 +6376,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466039</v>
+        <v>466066</v>
       </c>
       <c r="R42" t="n">
-        <v>7054631</v>
+        <v>7054397</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6478,7 +6478,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124232050</v>
+        <v>124237940</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6524,17 +6524,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466045</v>
+        <v>466040</v>
       </c>
       <c r="R43" t="n">
-        <v>7054447</v>
+        <v>7054768</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6630,7 +6630,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124228749</v>
+        <v>124235016</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6666,7 +6666,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6678,10 +6678,10 @@
         <v>466066</v>
       </c>
       <c r="R44" t="n">
-        <v>7054397</v>
+        <v>7054677</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124235016</v>
+        <v>124233675</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6813,7 +6813,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6822,13 +6822,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466066</v>
+        <v>466039</v>
       </c>
       <c r="R45" t="n">
-        <v>7054677</v>
+        <v>7054631</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124228388</v>
+        <v>124228589</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466017</v>
+        <v>466066</v>
       </c>
       <c r="R46" t="n">
-        <v>7054386</v>
+        <v>7054389</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124234049</v>
+        <v>124236910</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466057</v>
+        <v>466024</v>
       </c>
       <c r="R2" t="n">
-        <v>7054600</v>
+        <v>7054965</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124230947</v>
+        <v>124237831</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,55 +824,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466100</v>
+        <v>466048</v>
       </c>
       <c r="R3" t="n">
-        <v>7054439</v>
+        <v>7054795</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,6 +917,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1085,7 +1091,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124231227</v>
+        <v>124236835</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1121,17 +1127,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466082</v>
+        <v>466084</v>
       </c>
       <c r="R5" t="n">
-        <v>7054428</v>
+        <v>7054927</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,7 +1176,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1222,10 +1228,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124233935</v>
+        <v>124231227</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1238,39 +1244,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466049</v>
+        <v>466082</v>
       </c>
       <c r="R6" t="n">
-        <v>7054622</v>
+        <v>7054428</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1302,7 +1303,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1312,12 +1313,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,12 +1342,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1369,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124229168</v>
+        <v>124233335</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,60 +1377,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466061</v>
+        <v>466029</v>
       </c>
       <c r="R7" t="n">
-        <v>7054409</v>
+        <v>7054621</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1463,7 +1440,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1473,7 +1450,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1488,6 +1465,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1505,10 +1502,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124238716</v>
+        <v>124232343</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1521,37 +1518,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466019</v>
+        <v>466050</v>
       </c>
       <c r="R8" t="n">
-        <v>7054567</v>
+        <v>7054470</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1580,7 +1582,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1590,7 +1592,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1619,12 +1626,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1642,7 +1649,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124236542</v>
+        <v>124238072</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1678,17 +1685,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466114</v>
+        <v>466028</v>
       </c>
       <c r="R9" t="n">
-        <v>7054930</v>
+        <v>7054700</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1717,7 +1724,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1727,7 +1734,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1779,10 +1786,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124236835</v>
+        <v>124229168</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1791,41 +1798,60 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466084</v>
+        <v>466061</v>
       </c>
       <c r="R10" t="n">
-        <v>7054927</v>
+        <v>7054409</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1854,7 +1880,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1864,7 +1890,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1879,26 +1905,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1916,10 +1922,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124235081</v>
+        <v>124236594</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1928,46 +1934,60 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466058</v>
+        <v>466108</v>
       </c>
       <c r="R11" t="n">
-        <v>7054681</v>
+        <v>7054934</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1994,14 +2014,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2016,26 +2041,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124236233</v>
+        <v>124234435</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2069,37 +2074,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466113</v>
+        <v>466046</v>
       </c>
       <c r="R12" t="n">
-        <v>7054849</v>
+        <v>7054578</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2128,7 +2138,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2138,7 +2148,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2152,7 +2162,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2167,12 +2177,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2190,10 +2200,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124233335</v>
+        <v>124231450</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2206,37 +2216,56 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466029</v>
+        <v>466113</v>
       </c>
       <c r="R13" t="n">
-        <v>7054621</v>
+        <v>7054408</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2265,7 +2294,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2275,7 +2304,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2290,26 +2324,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2327,10 +2341,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124235507</v>
+        <v>124236233</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2343,42 +2357,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466047</v>
+        <v>466113</v>
       </c>
       <c r="R14" t="n">
-        <v>7054739</v>
+        <v>7054849</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2407,7 +2416,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2417,7 +2426,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2431,7 +2440,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2446,12 +2455,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2469,7 +2478,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124238072</v>
+        <v>124238954</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2509,13 +2518,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466028</v>
+        <v>466048</v>
       </c>
       <c r="R15" t="n">
-        <v>7054700</v>
+        <v>7054406</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2544,7 +2553,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2554,7 +2563,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2606,7 +2615,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124235851</v>
+        <v>124235290</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2642,17 +2651,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466040</v>
+        <v>466069</v>
       </c>
       <c r="R16" t="n">
-        <v>7054923</v>
+        <v>7054731</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2681,7 +2690,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2691,7 +2700,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2720,12 +2729,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2743,10 +2752,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124236594</v>
+        <v>124236542</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2755,60 +2764,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466108</v>
+        <v>466114</v>
       </c>
       <c r="R17" t="n">
-        <v>7054934</v>
+        <v>7054930</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2837,7 +2827,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2847,7 +2837,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2862,6 +2852,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2879,10 +2889,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124233387</v>
+        <v>124237519</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2895,42 +2905,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466025</v>
+        <v>466024</v>
       </c>
       <c r="R18" t="n">
-        <v>7054632</v>
+        <v>7054752</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2959,7 +2964,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2969,7 +2974,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2986,24 +2991,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3021,10 +3016,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124234435</v>
+        <v>124229492</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3037,39 +3032,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466046</v>
+        <v>466104</v>
       </c>
       <c r="R19" t="n">
-        <v>7054578</v>
+        <v>7054370</v>
       </c>
       <c r="S19" t="n">
         <v>7</v>
@@ -3101,7 +3091,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3111,7 +3101,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3140,12 +3130,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3163,10 +3153,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124238409</v>
+        <v>124235507</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3179,27 +3169,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3208,10 +3198,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466019</v>
+        <v>466047</v>
       </c>
       <c r="R20" t="n">
-        <v>7054696</v>
+        <v>7054739</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3243,7 +3233,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3253,12 +3243,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3310,7 +3295,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124237519</v>
+        <v>124234661</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -3350,13 +3335,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466024</v>
+        <v>466088</v>
       </c>
       <c r="R21" t="n">
-        <v>7054752</v>
+        <v>7054654</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3385,7 +3370,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3395,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3412,6 +3397,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM21" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3419,7 +3414,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3437,7 +3432,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124236910</v>
+        <v>124238716</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3473,14 +3468,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466024</v>
+        <v>466019</v>
       </c>
       <c r="R22" t="n">
-        <v>7054965</v>
+        <v>7054567</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3522,7 +3517,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3574,7 +3569,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124238954</v>
+        <v>124235851</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3610,17 +3605,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466048</v>
+        <v>466040</v>
       </c>
       <c r="R23" t="n">
-        <v>7054406</v>
+        <v>7054923</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3649,7 +3644,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3659,7 +3654,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124229492</v>
+        <v>124235081</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3727,34 +3722,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466104</v>
+        <v>466058</v>
       </c>
       <c r="R24" t="n">
-        <v>7054370</v>
+        <v>7054681</v>
       </c>
       <c r="S24" t="n">
         <v>7</v>
@@ -3784,19 +3784,14 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i två granhögstubbar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3825,12 +3820,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3848,10 +3843,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124234661</v>
+        <v>124230947</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3860,41 +3855,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466088</v>
+        <v>466100</v>
       </c>
       <c r="R25" t="n">
-        <v>7054654</v>
+        <v>7054439</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3923,7 +3932,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3933,7 +3942,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3948,26 +3957,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3985,10 +3974,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124235290</v>
+        <v>124238409</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4001,34 +3990,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466069</v>
+        <v>466019</v>
       </c>
       <c r="R26" t="n">
-        <v>7054731</v>
+        <v>7054696</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -4060,7 +4054,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4070,7 +4064,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4099,12 +4098,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4122,10 +4121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124231450</v>
+        <v>124233387</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4138,41 +4137,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4181,13 +4166,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466113</v>
+        <v>466025</v>
       </c>
       <c r="R27" t="n">
-        <v>7054408</v>
+        <v>7054632</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4216,7 +4201,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4226,12 +4211,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4246,6 +4226,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4263,7 +4263,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124232343</v>
+        <v>124233935</v>
       </c>
       <c r="B28" t="n">
         <v>91030</v>
@@ -4308,13 +4308,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466050</v>
+        <v>466049</v>
       </c>
       <c r="R28" t="n">
-        <v>7054470</v>
+        <v>7054622</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4410,7 +4410,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124237831</v>
+        <v>124234049</v>
       </c>
       <c r="B29" t="n">
         <v>91030</v>
@@ -4451,17 +4451,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466048</v>
+        <v>466057</v>
       </c>
       <c r="R29" t="n">
-        <v>7054795</v>
+        <v>7054600</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124235393</v>
+        <v>124232050</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4877,7 +4877,12 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4886,13 +4891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466051</v>
+        <v>466045</v>
       </c>
       <c r="R32" t="n">
-        <v>7054737</v>
+        <v>7054447</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4921,7 +4926,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4931,12 +4936,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,7 +4993,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124230274</v>
+        <v>124237940</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5027,19 +5032,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466120</v>
+        <v>466040</v>
       </c>
       <c r="R33" t="n">
-        <v>7054456</v>
+        <v>7054768</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5068,7 +5078,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5078,12 +5088,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5135,7 +5145,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124228388</v>
+        <v>124229096</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5169,24 +5179,27 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466017</v>
+        <v>466061</v>
       </c>
       <c r="R34" t="n">
-        <v>7054386</v>
+        <v>7054411</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5215,7 +5228,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5225,12 +5238,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5282,7 +5295,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124237622</v>
+        <v>124228749</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5318,22 +5331,22 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466053</v>
+        <v>466066</v>
       </c>
       <c r="R35" t="n">
-        <v>7054770</v>
+        <v>7054397</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5362,7 +5375,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5372,12 +5385,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5429,7 +5442,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124232050</v>
+        <v>124235016</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5465,12 +5478,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5479,13 +5487,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466045</v>
+        <v>466066</v>
       </c>
       <c r="R36" t="n">
-        <v>7054447</v>
+        <v>7054677</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5514,7 +5522,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5524,12 +5532,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5558,12 +5566,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5581,7 +5589,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124229096</v>
+        <v>124228589</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5615,27 +5623,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466061</v>
+        <v>466066</v>
       </c>
       <c r="R37" t="n">
-        <v>7054411</v>
+        <v>7054389</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5664,7 +5669,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5674,12 +5679,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5731,7 +5736,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124232609</v>
+        <v>124236498</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5765,31 +5770,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466085</v>
+        <v>466123</v>
       </c>
       <c r="R38" t="n">
-        <v>7054527</v>
+        <v>7054939</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5818,7 +5816,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5828,12 +5826,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5885,7 +5883,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124232959</v>
+        <v>124237622</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5924,24 +5922,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466071</v>
+        <v>466053</v>
       </c>
       <c r="R39" t="n">
-        <v>7054484</v>
+        <v>7054770</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5970,7 +5963,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5980,12 +5973,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6037,7 +6030,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124236498</v>
+        <v>124232959</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6076,16 +6069,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466123</v>
+        <v>466071</v>
       </c>
       <c r="R40" t="n">
-        <v>7054939</v>
+        <v>7054484</v>
       </c>
       <c r="S40" t="n">
         <v>12</v>
@@ -6117,7 +6115,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6127,12 +6125,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6184,7 +6182,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124231120</v>
+        <v>124230274</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6220,7 +6218,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6229,13 +6227,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466086</v>
+        <v>466120</v>
       </c>
       <c r="R41" t="n">
-        <v>7054427</v>
+        <v>7054456</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6264,7 +6262,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6274,12 +6272,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6331,7 +6329,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124228749</v>
+        <v>124228388</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6367,7 +6365,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6376,13 +6374,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466066</v>
+        <v>466017</v>
       </c>
       <c r="R42" t="n">
-        <v>7054397</v>
+        <v>7054386</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6411,7 +6409,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6421,12 +6419,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6478,7 +6476,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124237940</v>
+        <v>124233675</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6517,21 +6515,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466040</v>
+        <v>466039</v>
       </c>
       <c r="R43" t="n">
-        <v>7054768</v>
+        <v>7054631</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -6563,7 +6556,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,12 +6566,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6630,7 +6623,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124235016</v>
+        <v>124235393</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6675,13 +6668,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466066</v>
+        <v>466051</v>
       </c>
       <c r="R44" t="n">
-        <v>7054677</v>
+        <v>7054737</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6703,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6713,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6754,12 +6747,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6777,7 +6770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124233675</v>
+        <v>124231120</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6813,7 +6806,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6822,13 +6815,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466039</v>
+        <v>466086</v>
       </c>
       <c r="R45" t="n">
-        <v>7054631</v>
+        <v>7054427</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6850,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6860,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6917,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124228589</v>
+        <v>124232609</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6958,9 +6951,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466066</v>
+        <v>466085</v>
       </c>
       <c r="R46" t="n">
-        <v>7054389</v>
+        <v>7054527</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124232050</v>
+        <v>124228749</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4880,24 +4880,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466045</v>
+        <v>466066</v>
       </c>
       <c r="R32" t="n">
-        <v>7054447</v>
+        <v>7054397</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4926,7 +4921,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4936,12 +4931,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4993,7 +4988,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124237940</v>
+        <v>124236498</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5029,27 +5024,22 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466040</v>
+        <v>466123</v>
       </c>
       <c r="R33" t="n">
-        <v>7054768</v>
+        <v>7054939</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5078,7 +5068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5088,12 +5078,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5145,7 +5135,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124229096</v>
+        <v>124233675</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5179,27 +5169,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466061</v>
+        <v>466039</v>
       </c>
       <c r="R34" t="n">
-        <v>7054411</v>
+        <v>7054631</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5228,7 +5215,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5238,12 +5225,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5295,7 +5282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124228749</v>
+        <v>124235393</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5331,7 +5318,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5340,13 +5327,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466066</v>
+        <v>466051</v>
       </c>
       <c r="R35" t="n">
-        <v>7054397</v>
+        <v>7054737</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5375,7 +5362,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5385,12 +5372,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5442,7 +5429,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124235016</v>
+        <v>124232959</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5481,16 +5468,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466066</v>
+        <v>466071</v>
       </c>
       <c r="R36" t="n">
-        <v>7054677</v>
+        <v>7054484</v>
       </c>
       <c r="S36" t="n">
         <v>12</v>
@@ -5522,7 +5514,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5532,12 +5524,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5566,12 +5558,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5589,7 +5581,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124228589</v>
+        <v>124230274</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5625,7 +5617,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5634,13 +5626,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466066</v>
+        <v>466120</v>
       </c>
       <c r="R37" t="n">
-        <v>7054389</v>
+        <v>7054456</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5669,7 +5661,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5679,12 +5671,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5736,7 +5728,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124236498</v>
+        <v>124232609</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5770,24 +5762,31 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466123</v>
+        <v>466085</v>
       </c>
       <c r="R38" t="n">
-        <v>7054939</v>
+        <v>7054527</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5816,7 +5815,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5826,12 +5825,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5883,7 +5882,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124237622</v>
+        <v>124231120</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5924,17 +5923,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466053</v>
+        <v>466086</v>
       </c>
       <c r="R39" t="n">
-        <v>7054770</v>
+        <v>7054427</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5963,7 +5962,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5973,12 +5972,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6030,7 +6029,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124232959</v>
+        <v>124228388</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6069,24 +6068,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466071</v>
+        <v>466017</v>
       </c>
       <c r="R40" t="n">
-        <v>7054484</v>
+        <v>7054386</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6115,7 +6109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6125,12 +6119,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6182,7 +6176,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124230274</v>
+        <v>124228589</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6218,7 +6212,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6227,13 +6221,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466120</v>
+        <v>466066</v>
       </c>
       <c r="R41" t="n">
-        <v>7054456</v>
+        <v>7054389</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6262,7 +6256,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6272,12 +6266,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6329,7 +6323,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124228388</v>
+        <v>124235016</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6374,13 +6368,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466017</v>
+        <v>466066</v>
       </c>
       <c r="R42" t="n">
-        <v>7054386</v>
+        <v>7054677</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6409,7 +6403,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6419,12 +6413,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6453,12 +6447,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6476,7 +6470,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124233675</v>
+        <v>124237940</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6515,16 +6509,21 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466039</v>
+        <v>466040</v>
       </c>
       <c r="R43" t="n">
-        <v>7054631</v>
+        <v>7054768</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -6556,7 +6555,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6566,12 +6565,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6623,7 +6622,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124235393</v>
+        <v>124232050</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6659,7 +6658,12 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6668,13 +6672,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466051</v>
+        <v>466045</v>
       </c>
       <c r="R44" t="n">
-        <v>7054737</v>
+        <v>7054447</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6703,7 +6707,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6713,12 +6717,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6770,7 +6774,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124231120</v>
+        <v>124229096</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6804,24 +6808,27 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466086</v>
+        <v>466061</v>
       </c>
       <c r="R45" t="n">
-        <v>7054427</v>
+        <v>7054411</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6850,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6860,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6917,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124232609</v>
+        <v>124237622</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6951,28 +6958,21 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466085</v>
+        <v>466053</v>
       </c>
       <c r="R46" t="n">
-        <v>7054527</v>
+        <v>7054770</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124228749</v>
+        <v>124231120</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4877,7 +4877,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466066</v>
+        <v>466086</v>
       </c>
       <c r="R32" t="n">
-        <v>7054397</v>
+        <v>7054427</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,7 +4988,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124236498</v>
+        <v>124232050</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5024,22 +5024,27 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466123</v>
+        <v>466045</v>
       </c>
       <c r="R33" t="n">
-        <v>7054939</v>
+        <v>7054447</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5068,7 +5073,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5078,12 +5083,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5282,7 +5287,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124235393</v>
+        <v>124229096</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5316,24 +5321,27 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466051</v>
+        <v>466061</v>
       </c>
       <c r="R35" t="n">
-        <v>7054737</v>
+        <v>7054411</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5362,7 +5370,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5372,12 +5380,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5429,7 +5437,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124232959</v>
+        <v>124228589</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5468,24 +5476,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466071</v>
+        <v>466066</v>
       </c>
       <c r="R36" t="n">
-        <v>7054484</v>
+        <v>7054389</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5514,7 +5517,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5524,12 +5527,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5581,7 +5584,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124230274</v>
+        <v>124228388</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5617,7 +5620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5626,13 +5629,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466120</v>
+        <v>466017</v>
       </c>
       <c r="R37" t="n">
-        <v>7054456</v>
+        <v>7054386</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5661,7 +5664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5671,12 +5674,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5728,7 +5731,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124232609</v>
+        <v>124237940</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5762,8 +5765,6 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -5776,14 +5777,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466085</v>
+        <v>466040</v>
       </c>
       <c r="R38" t="n">
-        <v>7054527</v>
+        <v>7054768</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5815,7 +5816,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5825,12 +5826,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5882,7 +5883,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124231120</v>
+        <v>124232959</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5921,19 +5922,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466086</v>
+        <v>466071</v>
       </c>
       <c r="R39" t="n">
-        <v>7054427</v>
+        <v>7054484</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5962,7 +5968,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5972,12 +5978,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6029,7 +6035,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124228388</v>
+        <v>124237622</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6070,17 +6076,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466017</v>
+        <v>466053</v>
       </c>
       <c r="R40" t="n">
-        <v>7054386</v>
+        <v>7054770</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6109,7 +6115,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6119,12 +6125,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6176,7 +6182,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124228589</v>
+        <v>124235016</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6224,10 +6230,10 @@
         <v>466066</v>
       </c>
       <c r="R41" t="n">
-        <v>7054389</v>
+        <v>7054677</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6256,7 +6262,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6266,12 +6272,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6300,12 +6306,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6323,7 +6329,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124235016</v>
+        <v>124228749</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6359,7 +6365,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6371,10 +6377,10 @@
         <v>466066</v>
       </c>
       <c r="R42" t="n">
-        <v>7054677</v>
+        <v>7054397</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6403,7 +6409,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6413,12 +6419,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6447,12 +6453,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6470,7 +6476,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124237940</v>
+        <v>124232609</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6504,6 +6510,8 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -6516,14 +6524,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466040</v>
+        <v>466085</v>
       </c>
       <c r="R43" t="n">
-        <v>7054768</v>
+        <v>7054527</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -6555,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6565,12 +6573,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6622,7 +6630,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124232050</v>
+        <v>124235393</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6658,12 +6666,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6672,13 +6675,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466045</v>
+        <v>466051</v>
       </c>
       <c r="R44" t="n">
-        <v>7054447</v>
+        <v>7054737</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6707,7 +6710,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6717,12 +6720,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6774,7 +6777,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124229096</v>
+        <v>124236498</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6808,24 +6811,21 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466061</v>
+        <v>466123</v>
       </c>
       <c r="R45" t="n">
-        <v>7054411</v>
+        <v>7054939</v>
       </c>
       <c r="S45" t="n">
         <v>12</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124237622</v>
+        <v>124230274</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6960,22 +6960,22 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466053</v>
+        <v>466120</v>
       </c>
       <c r="R46" t="n">
-        <v>7054770</v>
+        <v>7054456</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124231120</v>
+        <v>124237622</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4882,17 +4882,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466086</v>
+        <v>466053</v>
       </c>
       <c r="R32" t="n">
-        <v>7054427</v>
+        <v>7054770</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,7 +4988,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124232050</v>
+        <v>124228388</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5024,12 +5024,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5038,13 +5033,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466045</v>
+        <v>466017</v>
       </c>
       <c r="R33" t="n">
-        <v>7054447</v>
+        <v>7054386</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5073,7 +5068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5083,12 +5078,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5140,7 +5135,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124233675</v>
+        <v>124236498</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5176,22 +5171,22 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466039</v>
+        <v>466123</v>
       </c>
       <c r="R34" t="n">
-        <v>7054631</v>
+        <v>7054939</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5220,7 +5215,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5230,12 +5225,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5287,7 +5282,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124229096</v>
+        <v>124228589</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5321,27 +5316,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466061</v>
+        <v>466066</v>
       </c>
       <c r="R35" t="n">
-        <v>7054411</v>
+        <v>7054389</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5370,7 +5362,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5380,12 +5372,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5437,7 +5429,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124228589</v>
+        <v>124232609</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5471,9 +5463,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5482,10 +5481,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466066</v>
+        <v>466085</v>
       </c>
       <c r="R36" t="n">
-        <v>7054389</v>
+        <v>7054527</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5517,7 +5516,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5527,12 +5526,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5584,7 +5583,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124228388</v>
+        <v>124229096</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5618,24 +5617,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466017</v>
+        <v>466061</v>
       </c>
       <c r="R37" t="n">
-        <v>7054386</v>
+        <v>7054411</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5664,7 +5666,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5674,12 +5676,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5731,7 +5733,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124237940</v>
+        <v>124235393</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5767,27 +5769,22 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466040</v>
+        <v>466051</v>
       </c>
       <c r="R38" t="n">
-        <v>7054768</v>
+        <v>7054737</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5816,7 +5813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5826,12 +5823,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5883,7 +5880,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124232959</v>
+        <v>124235016</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5922,21 +5919,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466071</v>
+        <v>466066</v>
       </c>
       <c r="R39" t="n">
-        <v>7054484</v>
+        <v>7054677</v>
       </c>
       <c r="S39" t="n">
         <v>12</v>
@@ -5968,7 +5960,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5978,12 +5970,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6012,12 +6004,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6035,7 +6027,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124237622</v>
+        <v>124233675</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6071,19 +6063,19 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466053</v>
+        <v>466039</v>
       </c>
       <c r="R40" t="n">
-        <v>7054770</v>
+        <v>7054631</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6115,7 +6107,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6125,12 +6117,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6182,7 +6174,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124235016</v>
+        <v>124232959</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6221,16 +6213,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466066</v>
+        <v>466071</v>
       </c>
       <c r="R41" t="n">
-        <v>7054677</v>
+        <v>7054484</v>
       </c>
       <c r="S41" t="n">
         <v>12</v>
@@ -6262,7 +6259,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6272,12 +6269,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6306,12 +6303,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6329,7 +6326,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124228749</v>
+        <v>124237940</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6368,19 +6365,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466066</v>
+        <v>466040</v>
       </c>
       <c r="R42" t="n">
-        <v>7054397</v>
+        <v>7054768</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6409,7 +6411,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6419,12 +6421,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6476,7 +6478,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124232609</v>
+        <v>124228749</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6510,31 +6512,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466085</v>
+        <v>466066</v>
       </c>
       <c r="R43" t="n">
-        <v>7054527</v>
+        <v>7054397</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6563,7 +6558,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,12 +6568,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6630,7 +6625,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124235393</v>
+        <v>124231120</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6675,13 +6670,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466051</v>
+        <v>466086</v>
       </c>
       <c r="R44" t="n">
-        <v>7054737</v>
+        <v>7054427</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6705,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6715,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6777,7 +6772,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124236498</v>
+        <v>124232050</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6813,22 +6808,27 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466123</v>
+        <v>466045</v>
       </c>
       <c r="R45" t="n">
-        <v>7054939</v>
+        <v>7054447</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4552,10 +4552,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124231714</v>
+        <v>124233428</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4568,27 +4568,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466077</v>
+        <v>466026</v>
       </c>
       <c r="R30" t="n">
-        <v>7054405</v>
+        <v>7054647</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4642,7 +4642,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4694,10 +4699,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124233428</v>
+        <v>124231714</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4710,27 +4715,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4739,13 +4744,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466026</v>
+        <v>466077</v>
       </c>
       <c r="R31" t="n">
-        <v>7054647</v>
+        <v>7054405</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4774,7 +4779,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4784,12 +4789,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124237622</v>
+        <v>124232609</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4875,21 +4875,28 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466053</v>
+        <v>466085</v>
       </c>
       <c r="R32" t="n">
-        <v>7054770</v>
+        <v>7054527</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4921,7 +4928,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4931,12 +4938,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,7 +4995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124228388</v>
+        <v>124231120</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5033,13 +5040,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466017</v>
+        <v>466086</v>
       </c>
       <c r="R33" t="n">
-        <v>7054386</v>
+        <v>7054427</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5068,7 +5075,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5078,12 +5085,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5135,7 +5142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124236498</v>
+        <v>124228749</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5171,22 +5178,22 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466123</v>
+        <v>466066</v>
       </c>
       <c r="R34" t="n">
-        <v>7054939</v>
+        <v>7054397</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5215,7 +5222,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5225,12 +5232,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5282,7 +5289,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124228589</v>
+        <v>124233675</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5318,7 +5325,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5327,10 +5334,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466066</v>
+        <v>466039</v>
       </c>
       <c r="R35" t="n">
-        <v>7054389</v>
+        <v>7054631</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -5362,7 +5369,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5372,12 +5379,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5429,7 +5436,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124232609</v>
+        <v>124235016</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5463,16 +5470,9 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5481,13 +5481,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466085</v>
+        <v>466066</v>
       </c>
       <c r="R36" t="n">
-        <v>7054527</v>
+        <v>7054677</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124229096</v>
+        <v>124228388</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5617,27 +5617,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466061</v>
+        <v>466017</v>
       </c>
       <c r="R37" t="n">
-        <v>7054411</v>
+        <v>7054386</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5666,7 +5663,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5676,12 +5673,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5880,7 +5877,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124235016</v>
+        <v>124230274</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5916,7 +5913,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5925,13 +5922,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466066</v>
+        <v>466120</v>
       </c>
       <c r="R39" t="n">
-        <v>7054677</v>
+        <v>7054456</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5960,7 +5957,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5970,12 +5967,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6004,12 +6001,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6027,7 +6024,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124233675</v>
+        <v>124229096</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6061,24 +6058,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466039</v>
+        <v>466061</v>
       </c>
       <c r="R40" t="n">
-        <v>7054631</v>
+        <v>7054411</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6174,7 +6174,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124232959</v>
+        <v>124237622</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6213,24 +6213,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466071</v>
+        <v>466053</v>
       </c>
       <c r="R41" t="n">
-        <v>7054484</v>
+        <v>7054770</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6259,7 +6254,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6269,12 +6264,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6326,7 +6321,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124237940</v>
+        <v>124236498</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6362,27 +6357,22 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466040</v>
+        <v>466123</v>
       </c>
       <c r="R42" t="n">
-        <v>7054768</v>
+        <v>7054939</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6411,7 +6401,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6421,12 +6411,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6478,7 +6468,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124228749</v>
+        <v>124232959</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6514,7 +6504,12 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6523,13 +6518,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466066</v>
+        <v>466071</v>
       </c>
       <c r="R43" t="n">
-        <v>7054397</v>
+        <v>7054484</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6558,7 +6553,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6568,12 +6563,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6625,7 +6620,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124231120</v>
+        <v>124237940</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6661,22 +6656,27 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466086</v>
+        <v>466040</v>
       </c>
       <c r="R44" t="n">
-        <v>7054427</v>
+        <v>7054768</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124230274</v>
+        <v>124228589</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6960,7 +6960,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466120</v>
+        <v>466066</v>
       </c>
       <c r="R46" t="n">
-        <v>7054456</v>
+        <v>7054389</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4552,10 +4552,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124233428</v>
+        <v>124231714</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4568,27 +4568,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466026</v>
+        <v>466077</v>
       </c>
       <c r="R30" t="n">
-        <v>7054647</v>
+        <v>7054405</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4642,12 +4642,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4699,10 +4694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124231714</v>
+        <v>124233428</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4715,27 +4710,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4744,13 +4739,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466077</v>
+        <v>466026</v>
       </c>
       <c r="R31" t="n">
-        <v>7054405</v>
+        <v>7054647</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4779,7 +4774,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4789,7 +4784,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124232609</v>
+        <v>124228388</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4875,16 +4875,9 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4893,13 +4886,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466085</v>
+        <v>466017</v>
       </c>
       <c r="R32" t="n">
-        <v>7054527</v>
+        <v>7054386</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4928,7 +4921,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4938,12 +4931,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4995,7 +4988,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124231120</v>
+        <v>124236498</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -5036,17 +5029,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466086</v>
+        <v>466123</v>
       </c>
       <c r="R33" t="n">
-        <v>7054427</v>
+        <v>7054939</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5075,7 +5068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5085,12 +5078,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5142,7 +5135,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124228749</v>
+        <v>124232959</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -5178,7 +5171,12 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5187,13 +5185,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466066</v>
+        <v>466071</v>
       </c>
       <c r="R34" t="n">
-        <v>7054397</v>
+        <v>7054484</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5222,7 +5220,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5232,12 +5230,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5289,7 +5287,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124233675</v>
+        <v>124230274</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -5334,13 +5332,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466039</v>
+        <v>466120</v>
       </c>
       <c r="R35" t="n">
-        <v>7054631</v>
+        <v>7054456</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5369,7 +5367,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5379,12 +5377,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5436,7 +5434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124235016</v>
+        <v>124232609</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -5470,9 +5468,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5481,13 +5486,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466066</v>
+        <v>466085</v>
       </c>
       <c r="R36" t="n">
-        <v>7054677</v>
+        <v>7054527</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5516,7 +5521,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5526,12 +5531,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5560,12 +5565,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5583,7 +5588,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124228388</v>
+        <v>124229096</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -5617,24 +5622,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466017</v>
+        <v>466061</v>
       </c>
       <c r="R37" t="n">
-        <v>7054386</v>
+        <v>7054411</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5663,7 +5671,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5673,12 +5681,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5730,7 +5738,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124235393</v>
+        <v>124228589</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5775,13 +5783,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466051</v>
+        <v>466066</v>
       </c>
       <c r="R38" t="n">
-        <v>7054737</v>
+        <v>7054389</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5810,7 +5818,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5820,7 +5828,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5877,7 +5885,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124230274</v>
+        <v>124228749</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5922,13 +5930,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466120</v>
+        <v>466066</v>
       </c>
       <c r="R39" t="n">
-        <v>7054456</v>
+        <v>7054397</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5957,7 +5965,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5967,12 +5975,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6024,7 +6032,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124229096</v>
+        <v>124235016</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -6058,24 +6066,21 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466061</v>
+        <v>466066</v>
       </c>
       <c r="R40" t="n">
-        <v>7054411</v>
+        <v>7054677</v>
       </c>
       <c r="S40" t="n">
         <v>12</v>
@@ -6107,7 +6112,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6117,12 +6122,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6151,12 +6156,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6174,7 +6179,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124237622</v>
+        <v>124237940</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -6210,7 +6215,12 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6219,10 +6229,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466053</v>
+        <v>466040</v>
       </c>
       <c r="R41" t="n">
-        <v>7054770</v>
+        <v>7054768</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -6254,7 +6264,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6264,12 +6274,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6321,7 +6331,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124236498</v>
+        <v>124232050</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -6357,22 +6367,27 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466123</v>
+        <v>466045</v>
       </c>
       <c r="R42" t="n">
-        <v>7054939</v>
+        <v>7054447</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6401,7 +6416,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6411,12 +6426,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6468,7 +6483,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124232959</v>
+        <v>124233675</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -6504,12 +6519,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6518,13 +6528,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466071</v>
+        <v>466039</v>
       </c>
       <c r="R43" t="n">
-        <v>7054484</v>
+        <v>7054631</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6553,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6563,12 +6573,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6620,7 +6630,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124237940</v>
+        <v>124237622</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -6656,12 +6666,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466040</v>
+        <v>466053</v>
       </c>
       <c r="R44" t="n">
-        <v>7054768</v>
+        <v>7054770</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6705,7 +6710,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6715,12 +6720,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6772,7 +6777,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124232050</v>
+        <v>124235393</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6808,12 +6813,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6822,13 +6822,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466045</v>
+        <v>466051</v>
       </c>
       <c r="R45" t="n">
-        <v>7054447</v>
+        <v>7054737</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124228589</v>
+        <v>124231120</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466066</v>
+        <v>466086</v>
       </c>
       <c r="R46" t="n">
-        <v>7054389</v>
+        <v>7054427</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4555,7 +4555,7 @@
         <v>124231714</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>124233428</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124228388</v>
+        <v>124228589</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466017</v>
+        <v>466066</v>
       </c>
       <c r="R32" t="n">
-        <v>7054386</v>
+        <v>7054389</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124236498</v>
+        <v>124233675</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5024,22 +5024,22 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466123</v>
+        <v>466039</v>
       </c>
       <c r="R33" t="n">
-        <v>7054939</v>
+        <v>7054631</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5135,10 +5135,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124232959</v>
+        <v>124228749</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5171,12 +5171,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5185,13 +5180,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466071</v>
+        <v>466066</v>
       </c>
       <c r="R34" t="n">
-        <v>7054484</v>
+        <v>7054397</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5220,7 +5215,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5230,12 +5225,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5287,10 +5282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124230274</v>
+        <v>124231120</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5323,7 +5318,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5332,13 +5327,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466120</v>
+        <v>466086</v>
       </c>
       <c r="R35" t="n">
-        <v>7054456</v>
+        <v>7054427</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5367,7 +5362,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5377,12 +5372,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5434,10 +5429,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124232609</v>
+        <v>124228388</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5468,16 +5463,9 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5486,13 +5474,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466085</v>
+        <v>466017</v>
       </c>
       <c r="R36" t="n">
-        <v>7054527</v>
+        <v>7054386</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5521,7 +5509,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5531,12 +5519,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5588,10 +5576,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124229096</v>
+        <v>124232609</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5626,23 +5614,27 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466061</v>
+        <v>466085</v>
       </c>
       <c r="R37" t="n">
-        <v>7054411</v>
+        <v>7054527</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5671,7 +5663,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5681,12 +5673,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5738,10 +5730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124228589</v>
+        <v>124230274</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5774,7 +5766,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5783,13 +5775,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466066</v>
+        <v>466120</v>
       </c>
       <c r="R38" t="n">
-        <v>7054389</v>
+        <v>7054456</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5818,7 +5810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5828,12 +5820,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5885,10 +5877,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124228749</v>
+        <v>124237622</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5921,22 +5913,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466066</v>
+        <v>466053</v>
       </c>
       <c r="R39" t="n">
-        <v>7054397</v>
+        <v>7054770</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5965,7 +5957,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5975,12 +5967,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6032,10 +6024,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124235016</v>
+        <v>124232050</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6068,7 +6060,12 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6077,13 +6074,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466066</v>
+        <v>466045</v>
       </c>
       <c r="R40" t="n">
-        <v>7054677</v>
+        <v>7054447</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6112,7 +6109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6122,12 +6119,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6156,12 +6153,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6182,7 +6179,7 @@
         <v>124237940</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6331,10 +6328,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124232050</v>
+        <v>124236498</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6367,27 +6364,22 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466045</v>
+        <v>466123</v>
       </c>
       <c r="R42" t="n">
-        <v>7054447</v>
+        <v>7054939</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6416,7 +6408,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6426,12 +6418,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6483,10 +6475,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124233675</v>
+        <v>124229096</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6517,24 +6509,27 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466039</v>
+        <v>466061</v>
       </c>
       <c r="R43" t="n">
-        <v>7054631</v>
+        <v>7054411</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6563,7 +6558,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6573,12 +6568,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6630,10 +6625,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124237622</v>
+        <v>124235016</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6671,17 +6666,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466053</v>
+        <v>466066</v>
       </c>
       <c r="R44" t="n">
-        <v>7054770</v>
+        <v>7054677</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6710,7 +6705,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6720,12 +6715,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6754,12 +6749,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6777,10 +6772,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124235393</v>
+        <v>124232959</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6816,19 +6811,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466051</v>
+        <v>466071</v>
       </c>
       <c r="R45" t="n">
-        <v>7054737</v>
+        <v>7054484</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,10 +6924,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124231120</v>
+        <v>124235393</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466086</v>
+        <v>466051</v>
       </c>
       <c r="R46" t="n">
-        <v>7054427</v>
+        <v>7054737</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -4841,7 +4841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124228589</v>
+        <v>124232609</v>
       </c>
       <c r="B32" t="n">
         <v>57635</v>
@@ -4875,9 +4875,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4886,10 +4893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466066</v>
+        <v>466085</v>
       </c>
       <c r="R32" t="n">
-        <v>7054389</v>
+        <v>7054527</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4921,7 +4928,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4931,12 +4938,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,7 +4995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124233675</v>
+        <v>124231120</v>
       </c>
       <c r="B33" t="n">
         <v>57635</v>
@@ -5024,7 +5031,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5033,13 +5040,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466039</v>
+        <v>466086</v>
       </c>
       <c r="R33" t="n">
-        <v>7054631</v>
+        <v>7054427</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5068,7 +5075,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5078,12 +5085,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5135,7 +5142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124228749</v>
+        <v>124232050</v>
       </c>
       <c r="B34" t="n">
         <v>57635</v>
@@ -5174,19 +5181,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466066</v>
+        <v>466045</v>
       </c>
       <c r="R34" t="n">
-        <v>7054397</v>
+        <v>7054447</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5215,7 +5227,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5225,12 +5237,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5282,7 +5294,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124231120</v>
+        <v>124228388</v>
       </c>
       <c r="B35" t="n">
         <v>57635</v>
@@ -5327,13 +5339,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466086</v>
+        <v>466017</v>
       </c>
       <c r="R35" t="n">
-        <v>7054427</v>
+        <v>7054386</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5362,7 +5374,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5372,12 +5384,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5429,7 +5441,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124228388</v>
+        <v>124237940</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
@@ -5465,22 +5477,27 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466017</v>
+        <v>466040</v>
       </c>
       <c r="R36" t="n">
-        <v>7054386</v>
+        <v>7054768</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5509,7 +5526,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5519,12 +5536,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5576,7 +5593,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124232609</v>
+        <v>124236498</v>
       </c>
       <c r="B37" t="n">
         <v>57635</v>
@@ -5610,31 +5627,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466085</v>
+        <v>466123</v>
       </c>
       <c r="R37" t="n">
-        <v>7054527</v>
+        <v>7054939</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5663,7 +5673,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5673,12 +5683,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5730,7 +5740,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124230274</v>
+        <v>124235016</v>
       </c>
       <c r="B38" t="n">
         <v>57635</v>
@@ -5766,7 +5776,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5775,13 +5785,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466120</v>
+        <v>466066</v>
       </c>
       <c r="R38" t="n">
-        <v>7054456</v>
+        <v>7054677</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5810,7 +5820,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5820,12 +5830,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5854,12 +5864,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -6024,7 +6034,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124232050</v>
+        <v>124229096</v>
       </c>
       <c r="B40" t="n">
         <v>57635</v>
@@ -6058,29 +6068,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466045</v>
+        <v>466061</v>
       </c>
       <c r="R40" t="n">
-        <v>7054447</v>
+        <v>7054411</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6109,7 +6117,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6119,12 +6127,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6176,7 +6184,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124237940</v>
+        <v>124235393</v>
       </c>
       <c r="B41" t="n">
         <v>57635</v>
@@ -6212,27 +6220,22 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466040</v>
+        <v>466051</v>
       </c>
       <c r="R41" t="n">
-        <v>7054768</v>
+        <v>7054737</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6261,7 +6264,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6271,12 +6274,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6328,7 +6331,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124236498</v>
+        <v>124232959</v>
       </c>
       <c r="B42" t="n">
         <v>57635</v>
@@ -6367,16 +6370,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466123</v>
+        <v>466071</v>
       </c>
       <c r="R42" t="n">
-        <v>7054939</v>
+        <v>7054484</v>
       </c>
       <c r="S42" t="n">
         <v>12</v>
@@ -6408,7 +6416,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6418,12 +6426,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6475,7 +6483,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124229096</v>
+        <v>124230274</v>
       </c>
       <c r="B43" t="n">
         <v>57635</v>
@@ -6509,27 +6517,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466061</v>
+        <v>466120</v>
       </c>
       <c r="R43" t="n">
-        <v>7054411</v>
+        <v>7054456</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6558,7 +6563,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6568,12 +6573,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6625,7 +6630,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124235016</v>
+        <v>124228589</v>
       </c>
       <c r="B44" t="n">
         <v>57635</v>
@@ -6673,10 +6678,10 @@
         <v>466066</v>
       </c>
       <c r="R44" t="n">
-        <v>7054677</v>
+        <v>7054389</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6705,7 +6710,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6715,12 +6720,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6749,12 +6754,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6772,7 +6777,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124232959</v>
+        <v>124233675</v>
       </c>
       <c r="B45" t="n">
         <v>57635</v>
@@ -6808,12 +6813,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6822,13 +6822,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466071</v>
+        <v>466039</v>
       </c>
       <c r="R45" t="n">
-        <v>7054484</v>
+        <v>7054631</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6924,7 +6924,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124235393</v>
+        <v>124228749</v>
       </c>
       <c r="B46" t="n">
         <v>57635</v>
@@ -6960,7 +6960,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466051</v>
+        <v>466066</v>
       </c>
       <c r="R46" t="n">
-        <v>7054737</v>
+        <v>7054397</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124236910</v>
+        <v>87776208</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>698</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Risgårdsvägen, 780 m NV om bro för väg 340 Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466024</v>
+        <v>466043</v>
       </c>
       <c r="R2" t="n">
-        <v>7054965</v>
+        <v>7054270</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>117 plantor, alla höga med mörkt blå blommor. På båda sidor av vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,98 +772,80 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vägkant grusväg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124237831</v>
+        <v>111915844</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>698</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Risgårdsvägen, 800 m NV om bro över Åkerån väg 340, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466048</v>
+        <v>466044</v>
       </c>
       <c r="R3" t="n">
-        <v>7054795</v>
+        <v>7054265</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,22 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Detalj. Alla blå och höga - all time high. V sidan av vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,62 +888,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124233251</v>
+        <v>124229492</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -994,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466029</v>
+        <v>466104</v>
       </c>
       <c r="R4" t="n">
-        <v>7054550</v>
+        <v>7054370</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1091,19 +1039,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124236835</v>
+        <v>124231227</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1127,17 +1070,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466084</v>
+        <v>466082</v>
       </c>
       <c r="R5" t="n">
-        <v>7054927</v>
+        <v>7054428</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1166,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1176,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1228,19 +1171,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124231227</v>
+        <v>124233251</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1268,13 +1206,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466082</v>
+        <v>466029</v>
       </c>
       <c r="R6" t="n">
-        <v>7054428</v>
+        <v>7054550</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1303,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1313,7 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1368,16 +1306,11 @@
         <v>124233335</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1502,58 +1435,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124232343</v>
+        <v>124234661</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466050</v>
+        <v>466088</v>
       </c>
       <c r="R8" t="n">
-        <v>7054470</v>
+        <v>7054654</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1582,7 +1505,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1592,12 +1515,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I en granhögstubbe med bohålsliknande hackspår.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,12 +1544,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1649,19 +1567,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124238072</v>
+        <v>124235290</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1689,13 +1602,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466028</v>
+        <v>466069</v>
       </c>
       <c r="R9" t="n">
-        <v>7054700</v>
+        <v>7054731</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1724,7 +1637,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1734,7 +1647,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1763,12 +1676,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1786,72 +1699,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124229168</v>
+        <v>124235851</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466061</v>
+        <v>466040</v>
       </c>
       <c r="R10" t="n">
-        <v>7054409</v>
+        <v>7054923</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1880,7 +1769,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1890,7 +1779,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1905,6 +1794,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1922,72 +1831,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124236594</v>
+        <v>124236233</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466108</v>
+        <v>466113</v>
       </c>
       <c r="R11" t="n">
-        <v>7054934</v>
+        <v>7054849</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2016,7 +1901,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2026,7 +1911,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2040,7 +1925,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2058,58 +1963,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124234435</v>
+        <v>124236542</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466046</v>
+        <v>466114</v>
       </c>
       <c r="R12" t="n">
-        <v>7054578</v>
+        <v>7054930</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2138,7 +2033,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2148,7 +2043,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2177,12 +2072,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2200,72 +2095,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124231450</v>
+        <v>124236835</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466113</v>
+        <v>466084</v>
       </c>
       <c r="R13" t="n">
-        <v>7054408</v>
+        <v>7054927</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2294,7 +2165,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2304,12 +2175,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I bitvis flerskiktad äldre granskog.</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2324,6 +2190,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2341,19 +2227,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124236233</v>
+        <v>124236910</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2377,17 +2258,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466113</v>
+        <v>466024</v>
       </c>
       <c r="R14" t="n">
-        <v>7054849</v>
+        <v>7054965</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2416,7 +2297,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2426,7 +2307,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2440,7 +2321,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2478,19 +2359,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124238954</v>
+        <v>124237519</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2518,13 +2394,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466048</v>
+        <v>466024</v>
       </c>
       <c r="R15" t="n">
-        <v>7054406</v>
+        <v>7054752</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2553,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2563,7 +2439,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2580,16 +2456,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM15" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2597,7 +2463,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2615,19 +2481,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124235290</v>
+        <v>124238072</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2655,13 +2516,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466069</v>
+        <v>466028</v>
       </c>
       <c r="R16" t="n">
-        <v>7054731</v>
+        <v>7054700</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2690,7 +2551,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2700,7 +2561,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2729,12 +2590,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2752,19 +2613,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124236542</v>
+        <v>124238716</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2788,17 +2644,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466114</v>
+        <v>466019</v>
       </c>
       <c r="R17" t="n">
-        <v>7054930</v>
+        <v>7054567</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2827,7 +2683,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2837,7 +2693,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2889,19 +2745,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124237519</v>
+        <v>124238954</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2929,13 +2780,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466024</v>
+        <v>466048</v>
       </c>
       <c r="R18" t="n">
-        <v>7054752</v>
+        <v>7054406</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2964,7 +2815,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2974,7 +2825,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2991,6 +2842,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM18" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2998,7 +2859,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3016,53 +2877,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124229492</v>
+        <v>124233428</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466104</v>
+        <v>466026</v>
       </c>
       <c r="R19" t="n">
-        <v>7054370</v>
+        <v>7054647</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3091,7 +2952,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3101,7 +2962,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,12 +2996,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3153,43 +3019,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124235507</v>
+        <v>124238409</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3198,10 +3059,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466047</v>
+        <v>466019</v>
       </c>
       <c r="R20" t="n">
-        <v>7054739</v>
+        <v>7054696</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3233,7 +3094,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3243,7 +3104,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,15 +3161,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124234661</v>
+        <v>124228388</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3311,37 +3172,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466088</v>
+        <v>466017</v>
       </c>
       <c r="R21" t="n">
-        <v>7054654</v>
+        <v>7054386</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3370,7 +3236,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3380,7 +3246,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid myrstack.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3409,12 +3280,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3432,15 +3303,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124238716</v>
+        <v>124228589</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3448,37 +3314,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466019</v>
+        <v>466066</v>
       </c>
       <c r="R22" t="n">
-        <v>7054567</v>
+        <v>7054389</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3507,7 +3378,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3517,7 +3388,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3546,12 +3422,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3569,15 +3445,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124235851</v>
+        <v>124228749</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3585,37 +3456,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466040</v>
+        <v>466066</v>
       </c>
       <c r="R23" t="n">
-        <v>7054923</v>
+        <v>7054397</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3644,7 +3520,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3654,7 +3530,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3683,12 +3564,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3706,15 +3587,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124235081</v>
+        <v>124229096</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3722,42 +3598,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466058</v>
+        <v>466061</v>
       </c>
       <c r="R24" t="n">
-        <v>7054681</v>
+        <v>7054411</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3784,14 +3663,24 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Fruktkroppar i två granhögstubbar.</t>
+          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3820,12 +3709,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3843,32 +3732,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124230947</v>
+        <v>124230274</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3876,19 +3760,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3897,13 +3772,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466100</v>
+        <v>466120</v>
       </c>
       <c r="R25" t="n">
-        <v>7054439</v>
+        <v>7054456</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3932,7 +3807,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3942,7 +3817,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3957,6 +3837,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3974,15 +3874,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124238409</v>
+        <v>124231120</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3990,16 +3885,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4019,13 +3914,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466019</v>
+        <v>466086</v>
       </c>
       <c r="R26" t="n">
-        <v>7054696</v>
+        <v>7054427</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4054,7 +3949,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4064,12 +3959,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre hackspår i basen av en tvåstammig gran och en granstubbe.</t>
+          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4121,15 +4016,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124233387</v>
+        <v>124232050</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4137,27 +4027,32 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4166,13 +4061,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466025</v>
+        <v>466045</v>
       </c>
       <c r="R27" t="n">
-        <v>7054632</v>
+        <v>7054447</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4201,7 +4096,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4211,7 +4106,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4240,12 +4140,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4263,15 +4163,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124233935</v>
+        <v>124232609</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4279,27 +4174,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4308,10 +4210,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466049</v>
+        <v>466085</v>
       </c>
       <c r="R28" t="n">
-        <v>7054622</v>
+        <v>7054527</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4343,7 +4245,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4353,12 +4255,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en högstubbe som är lämplig för bohål åt tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4387,12 +4289,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4410,15 +4312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124234049</v>
+        <v>124232959</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4426,27 +4323,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4455,13 +4357,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466057</v>
+        <v>466071</v>
       </c>
       <c r="R29" t="n">
-        <v>7054600</v>
+        <v>7054484</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4490,7 +4392,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4500,7 +4402,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4529,12 +4436,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4552,15 +4459,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124231714</v>
+        <v>124233675</v>
       </c>
       <c r="B30" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4568,27 +4470,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4597,13 +4499,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466077</v>
+        <v>466039</v>
       </c>
       <c r="R30" t="n">
-        <v>7054405</v>
+        <v>7054631</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4632,7 +4534,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4642,7 +4544,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4694,15 +4601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124233428</v>
+        <v>124235016</v>
       </c>
       <c r="B31" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4710,16 +4612,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4730,7 +4632,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4739,13 +4641,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466026</v>
+        <v>466066</v>
       </c>
       <c r="R31" t="n">
-        <v>7054647</v>
+        <v>7054677</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4774,7 +4676,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4784,12 +4686,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4818,12 +4720,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4841,10 +4743,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124228589</v>
+        <v>124235393</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4881,13 +4783,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466066</v>
+        <v>466051</v>
       </c>
       <c r="R32" t="n">
-        <v>7054389</v>
+        <v>7054737</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4916,7 +4818,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4926,7 +4828,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4983,10 +4885,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124232609</v>
+        <v>124236498</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5012,31 +4914,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466085</v>
+        <v>466123</v>
       </c>
       <c r="R33" t="n">
-        <v>7054527</v>
+        <v>7054939</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5065,7 +4960,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5075,12 +4970,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en tvåstammig gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5132,10 +5027,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124231120</v>
+        <v>124237622</v>
       </c>
       <c r="B34" t="n">
-        <v>57635</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5168,17 +5063,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Öretjärnen, Öretjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466086</v>
+        <v>466053</v>
       </c>
       <c r="R34" t="n">
-        <v>7054427</v>
+        <v>7054770</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5207,7 +5102,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5217,12 +5112,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med kådaflöden.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5277,7 +5172,7 @@
         <v>124237940</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5421,27 +5316,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124230274</v>
+        <v>124229168</v>
       </c>
       <c r="B36" t="n">
-        <v>57635</v>
+        <v>58327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5449,10 +5344,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5461,13 +5370,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466120</v>
+        <v>466061</v>
       </c>
       <c r="R36" t="n">
-        <v>7054456</v>
+        <v>7054409</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5496,7 +5405,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5506,12 +5415,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam med kådaflöden.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5526,26 +5430,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5563,27 +5447,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124236498</v>
+        <v>124230947</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
+        <v>58327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5591,25 +5475,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466123</v>
+        <v>466100</v>
       </c>
       <c r="R37" t="n">
-        <v>7054939</v>
+        <v>7054439</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5638,7 +5531,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5648,12 +5541,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5668,26 +5556,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5705,27 +5573,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124235393</v>
+        <v>124236594</v>
       </c>
       <c r="B38" t="n">
-        <v>57635</v>
+        <v>58327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5733,25 +5601,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
+          <t>Nils-Perstjärnen, Nils-Perstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466051</v>
+        <v>466108</v>
       </c>
       <c r="R38" t="n">
-        <v>7054737</v>
+        <v>7054934</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5780,7 +5662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5790,12 +5672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5810,26 +5687,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5847,10 +5704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124228749</v>
+        <v>124231450</v>
       </c>
       <c r="B39" t="n">
-        <v>57635</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5858,27 +5715,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5887,13 +5758,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466066</v>
+        <v>466113</v>
       </c>
       <c r="R39" t="n">
-        <v>7054397</v>
+        <v>7054408</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5922,7 +5793,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5932,12 +5803,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs minst 6 meter på en något grövre granstam.</t>
+          <t>I bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5952,26 +5823,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5986,1013 +5837,6 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>124232959</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>466071</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7054484</v>
-      </c>
-      <c r="S40" t="n">
-        <v>12</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre men möjligen även färska ringhack (gränsfall).</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>124228388</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>466017</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7054386</v>
-      </c>
-      <c r="S41" t="n">
-        <v>7</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid myrstack.</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>124232050</v>
-      </c>
-      <c r="B42" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>466045</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7054447</v>
-      </c>
-      <c r="S42" t="n">
-        <v>8</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, med några färska bland metervis av äldre ringhack på en något grövre gran.</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>124229096</v>
-      </c>
-      <c r="B43" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>466061</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7054411</v>
-      </c>
-      <c r="S43" t="n">
-        <v>12</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, där de yngsta ringhacken bedöms vara 5 - 10 år gamla.</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>124235016</v>
-      </c>
-      <c r="B44" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>466066</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7054677</v>
-      </c>
-      <c r="S44" t="n">
-        <v>12</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe med granticka.</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>124237622</v>
-      </c>
-      <c r="B45" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Öretjärnen, Öretjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>466053</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7054770</v>
-      </c>
-      <c r="S45" t="n">
-        <v>9</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>124233675</v>
-      </c>
-      <c r="B46" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>466039</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7054631</v>
-      </c>
-      <c r="S46" t="n">
-        <v>9</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16978-2025 artfynd.xlsx
+++ b/artfynd/A 16978-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87776208</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111915844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124229492</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1168,6 +1188,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124231227</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1300,6 +1325,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124233251</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1432,6 +1462,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124233335</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1564,6 +1599,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124234661</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1696,6 +1736,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124235290</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1828,6 +1873,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124235851</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1960,6 +2010,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124236233</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2092,6 +2147,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124236542</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2224,6 +2284,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124236835</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2356,6 +2421,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124236910</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2478,6 +2548,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124237519</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2610,6 +2685,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124238072</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2742,6 +2822,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124238716</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2874,6 +2959,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124238954</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3016,6 +3106,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124233428</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3158,6 +3253,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124238409</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3300,6 +3400,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124228388</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3442,6 +3547,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124228589</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3584,6 +3694,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124228749</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3729,6 +3844,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124229096</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3871,6 +3991,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124230274</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4013,6 +4138,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124231120</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4160,6 +4290,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124232050</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4309,6 +4444,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124232609</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4456,6 +4596,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124232959</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4598,6 +4743,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124233675</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4740,6 +4890,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124235016</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4882,6 +5037,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124235393</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5024,6 +5184,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124236498</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5166,6 +5331,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124237622</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5313,6 +5483,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124237940</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5444,6 +5619,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124229168</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5570,6 +5750,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124230947</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5701,6 +5886,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124236594</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5837,8 +6027,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124231450</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>